--- a/templates/03_Venue_Details_Template.xlsx
+++ b/templates/03_Venue_Details_Template.xlsx
@@ -2,8 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="1" r:id="R7da48fdf36854f75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ramp Up" sheetId="2" r:id="R4a1e7b5e260c4069"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="1" r:id="R6ff7550de8f64d3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ramp Up" sheetId="2" r:id="R9478b6ac53444b5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Growth" sheetId="3" r:id="Rfc1abc6206b849d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="New Venues" sheetId="4" r:id="Rfa93236b691f4574"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="200" formatCode="0%"/>
+    <x:numFmt numFmtId="201" formatCode="0.0"/>
+    <x:numFmt numFmtId="202" formatCode="$#,##0"/>
   </x:numFmts>
   <x:fonts count="4">
     <x:font>
@@ -58,7 +62,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="9">
+  <x:cellXfs count="11">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -76,6 +80,12 @@
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -653,1141 +663,1141 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="7" t="str">
-        <x:v>Yo-Chi Charlestown</x:v>
+        <x:v>Yo-Chi Chatswood</x:v>
       </x:c>
       <x:c r="B15" s="7" t="str">
         <x:v>NSW</x:v>
       </x:c>
       <x:c r="C15" s="7" t="str">
-        <x:v>2025-10-05</x:v>
+        <x:v>2025-09-19</x:v>
       </x:c>
       <x:c r="D15" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E15" s="7" t="str">
-        <x:v>Tenancy L01 1036, South Piazza, Charlestown square</x:v>
+        <x:v>350 Victoria Street, Chatswood NSW 2067</x:v>
       </x:c>
       <x:c r="F15" s="7" t="str">
-        <x:v>Charlestown</x:v>
+        <x:v>Chatswood</x:v>
       </x:c>
       <x:c r="G15" s="7" t="n">
-        <x:v>2290</x:v>
+        <x:v>2067</x:v>
       </x:c>
       <x:c r="H15" s="7" t="str">
-        <x:v>02 4996 4184</x:v>
+        <x:v>02 9058 0701</x:v>
       </x:c>
       <x:c r="I15" s="7" t="str">
-        <x:v>charlestown@yochi.com.au</x:v>
+        <x:v>chatswood@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="7" t="str">
-        <x:v>Yo-Chi Chatswood</x:v>
+        <x:v>Yo-Chi Chevron Surfers Paradise</x:v>
       </x:c>
       <x:c r="B16" s="7" t="str">
-        <x:v>NSW</x:v>
+        <x:v>QLD</x:v>
       </x:c>
       <x:c r="C16" s="7" t="str">
-        <x:v>2025-09-19</x:v>
+        <x:v>2023-08-14</x:v>
       </x:c>
       <x:c r="D16" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E16" s="7" t="str">
-        <x:v>350 Victoria Street, Chatswood NSW 2067</x:v>
+        <x:v>11/3240 Surfers Paradise Blvd</x:v>
       </x:c>
       <x:c r="F16" s="7" t="str">
-        <x:v>Chatswood</x:v>
+        <x:v>Surfers Paradise</x:v>
       </x:c>
       <x:c r="G16" s="7" t="n">
-        <x:v>2067</x:v>
+        <x:v>4217</x:v>
       </x:c>
       <x:c r="H16" s="7" t="str">
-        <x:v>02 9058 0701</x:v>
+        <x:v>07 3010 8524</x:v>
       </x:c>
       <x:c r="I16" s="7" t="str">
-        <x:v>chatswood@yochi.com.au</x:v>
+        <x:v>surfersparadise@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="7" t="str">
-        <x:v>Yo-Chi Chevron Surfers Paradise</x:v>
+        <x:v>Yo-Chi Chippendale</x:v>
       </x:c>
       <x:c r="B17" s="7" t="str">
-        <x:v>QLD</x:v>
+        <x:v>NSW</x:v>
       </x:c>
       <x:c r="C17" s="7" t="str">
-        <x:v>2023-08-14</x:v>
+        <x:v>2025-12-13</x:v>
       </x:c>
       <x:c r="D17" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E17" s="7" t="str">
-        <x:v>11/3240 Surfers Paradise Blvd</x:v>
+        <x:v>38 Broadway, Chippendale NSW 2008</x:v>
       </x:c>
       <x:c r="F17" s="7" t="str">
-        <x:v>Surfers Paradise</x:v>
+        <x:v>Chippendale</x:v>
       </x:c>
       <x:c r="G17" s="7" t="n">
-        <x:v>4217</x:v>
+        <x:v>2008</x:v>
       </x:c>
       <x:c r="H17" s="7" t="str">
-        <x:v>07 3010 8524</x:v>
+        <x:v>02 8089 0395</x:v>
       </x:c>
       <x:c r="I17" s="7" t="str">
-        <x:v>surfersparadise@yochi.com.au</x:v>
+        <x:v>chippendale@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="7" t="str">
-        <x:v>Yo-Chi Chippendale</x:v>
+        <x:v>Yo-Chi Circular Quay</x:v>
       </x:c>
       <x:c r="B18" s="7" t="str">
         <x:v>NSW</x:v>
       </x:c>
       <x:c r="C18" s="7" t="str">
-        <x:v>2025-12-13</x:v>
+        <x:v>2025-03-25</x:v>
       </x:c>
       <x:c r="D18" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E18" s="7" t="str">
-        <x:v>38 Broadway, Chippendale NSW 2008</x:v>
+        <x:v>Tenancy 05-13, Alfred St, Gateway Plaza, 1 Macquarie Place</x:v>
       </x:c>
       <x:c r="F18" s="7" t="str">
-        <x:v>Chippendale</x:v>
+        <x:v>Sydney</x:v>
       </x:c>
       <x:c r="G18" s="7" t="n">
-        <x:v>2008</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="H18" s="7" t="str">
-        <x:v>02 8089 0395</x:v>
+        <x:v>02 9139 1009</x:v>
       </x:c>
       <x:c r="I18" s="7" t="str">
-        <x:v>chippendale@yochi.com.au</x:v>
+        <x:v>circularquay@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="7" t="str">
-        <x:v>Yo-Chi Circular Quay</x:v>
+        <x:v>Yo-Chi Claremont</x:v>
       </x:c>
       <x:c r="B19" s="7" t="str">
-        <x:v>NSW</x:v>
+        <x:v>WA</x:v>
       </x:c>
       <x:c r="C19" s="7" t="str">
-        <x:v>2025-03-25</x:v>
+        <x:v>2025-05-11</x:v>
       </x:c>
       <x:c r="D19" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E19" s="7" t="str">
-        <x:v>Tenancy 05-13, Alfred St, Gateway Plaza, 1 Macquarie Place</x:v>
+        <x:v>L1.117A 9 Bay View Terrace, Claremont WA 6010</x:v>
       </x:c>
       <x:c r="F19" s="7" t="str">
-        <x:v>Sydney</x:v>
+        <x:v>Claremont</x:v>
       </x:c>
       <x:c r="G19" s="7" t="n">
-        <x:v>2000</x:v>
+        <x:v>6010</x:v>
       </x:c>
       <x:c r="H19" s="7" t="str">
-        <x:v>02 9139 1009</x:v>
+        <x:v>08 6364 0048</x:v>
       </x:c>
       <x:c r="I19" s="7" t="str">
-        <x:v>circularquay@yochi.com.au</x:v>
+        <x:v>claremont@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="7" t="str">
-        <x:v>Yo-Chi Claremont</x:v>
+        <x:v>Yo-Chi Cockburn Central</x:v>
       </x:c>
       <x:c r="B20" s="7" t="str">
         <x:v>WA</x:v>
       </x:c>
       <x:c r="C20" s="7" t="str">
-        <x:v>2025-05-11</x:v>
+        <x:v>2025-06-27</x:v>
       </x:c>
       <x:c r="D20" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E20" s="7" t="str">
-        <x:v>L1.117A 9 Bay View Terrace, Claremont WA 6010</x:v>
+        <x:v>Unit No. R-006, Cockburn Gateway Shopping Centre, 816 Beeliar Dr</x:v>
       </x:c>
       <x:c r="F20" s="7" t="str">
-        <x:v>Claremont</x:v>
+        <x:v>Success</x:v>
       </x:c>
       <x:c r="G20" s="7" t="n">
-        <x:v>6010</x:v>
+        <x:v>6164</x:v>
       </x:c>
       <x:c r="H20" s="7" t="str">
-        <x:v>08 6364 0048</x:v>
+        <x:v>08 6364 0033</x:v>
       </x:c>
       <x:c r="I20" s="7" t="str">
-        <x:v>claremont@yochi.com.au</x:v>
+        <x:v>cockburn@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="7" t="str">
-        <x:v>Yo-Chi Cockburn Central</x:v>
+        <x:v>Yo-Chi Coogee</x:v>
       </x:c>
       <x:c r="B21" s="7" t="str">
-        <x:v>WA</x:v>
+        <x:v>NSW</x:v>
       </x:c>
       <x:c r="C21" s="7" t="str">
-        <x:v>2025-06-27</x:v>
+        <x:v>2024-10-01</x:v>
       </x:c>
       <x:c r="D21" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E21" s="7" t="str">
-        <x:v>Unit No. R-006, Cockburn Gateway Shopping Centre, 816 Beeliar Dr</x:v>
+        <x:v>235 Coogee Bay Road,</x:v>
       </x:c>
       <x:c r="F21" s="7" t="str">
-        <x:v>Success</x:v>
+        <x:v>Coogee</x:v>
       </x:c>
       <x:c r="G21" s="7" t="n">
-        <x:v>6164</x:v>
+        <x:v>2034</x:v>
       </x:c>
       <x:c r="H21" s="7" t="str">
-        <x:v>08 6364 0033</x:v>
+        <x:v>02 8866 2835</x:v>
       </x:c>
       <x:c r="I21" s="7" t="str">
-        <x:v>cockburn@yochi.com.au</x:v>
+        <x:v>coogee@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="7" t="str">
-        <x:v>Yo-Chi Coogee</x:v>
+        <x:v>Yo-Chi Cronulla</x:v>
       </x:c>
       <x:c r="B22" s="7" t="str">
         <x:v>NSW</x:v>
       </x:c>
       <x:c r="C22" s="7" t="str">
-        <x:v>2024-10-01</x:v>
+        <x:v>2025-07-07</x:v>
       </x:c>
       <x:c r="D22" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E22" s="7" t="str">
-        <x:v>235 Coogee Bay Road,</x:v>
+        <x:v>43 Cronulla Street</x:v>
       </x:c>
       <x:c r="F22" s="7" t="str">
-        <x:v>Coogee</x:v>
+        <x:v>Cronulla</x:v>
       </x:c>
       <x:c r="G22" s="7" t="n">
-        <x:v>2034</x:v>
+        <x:v>2230</x:v>
       </x:c>
       <x:c r="H22" s="7" t="str">
-        <x:v>02 8866 2835</x:v>
+        <x:v>02 9227 4525</x:v>
       </x:c>
       <x:c r="I22" s="7" t="str">
-        <x:v>coogee@yochi.com.au</x:v>
+        <x:v>cronulla@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="7" t="str">
-        <x:v>Yo-Chi Cronulla</x:v>
+        <x:v>Yo-Chi Currambine</x:v>
       </x:c>
       <x:c r="B23" s="7" t="str">
-        <x:v>NSW</x:v>
+        <x:v>WA</x:v>
       </x:c>
       <x:c r="C23" s="7" t="str">
-        <x:v>2025-07-07</x:v>
+        <x:v>2024-11-28</x:v>
       </x:c>
       <x:c r="D23" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E23" s="7" t="str">
-        <x:v>43 Cronulla Street</x:v>
+        <x:v>Tenancy SP104, Currambine Central 1244 Marmion ave</x:v>
       </x:c>
       <x:c r="F23" s="7" t="str">
-        <x:v>Cronulla</x:v>
+        <x:v>Currambine</x:v>
       </x:c>
       <x:c r="G23" s="7" t="n">
-        <x:v>2230</x:v>
+        <x:v>6028</x:v>
       </x:c>
       <x:c r="H23" s="7" t="str">
-        <x:v>02 9227 4525</x:v>
+        <x:v>08 6323 5441</x:v>
       </x:c>
       <x:c r="I23" s="7" t="str">
-        <x:v>cronulla@yochi.com.au</x:v>
+        <x:v>currambine@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="7" t="str">
-        <x:v>Yo-Chi Currambine</x:v>
+        <x:v>Yo-Chi Double Bay</x:v>
       </x:c>
       <x:c r="B24" s="7" t="str">
-        <x:v>WA</x:v>
+        <x:v>NSW</x:v>
       </x:c>
       <x:c r="C24" s="7" t="str">
-        <x:v>2024-11-28</x:v>
+        <x:v>2024-09-17</x:v>
       </x:c>
       <x:c r="D24" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E24" s="7" t="str">
-        <x:v>Tenancy SP104, Currambine Central 1244 Marmion ave</x:v>
+        <x:v>Shop 16, Kiaora Place,</x:v>
       </x:c>
       <x:c r="F24" s="7" t="str">
-        <x:v>Currambine</x:v>
+        <x:v>Double Bay</x:v>
       </x:c>
       <x:c r="G24" s="7" t="n">
-        <x:v>6028</x:v>
+        <x:v>2028</x:v>
       </x:c>
       <x:c r="H24" s="7" t="str">
-        <x:v>08 6323 5441</x:v>
+        <x:v>02 8338 7726</x:v>
       </x:c>
       <x:c r="I24" s="7" t="str">
-        <x:v>currambine@yochi.com.au</x:v>
+        <x:v>doublebay@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="7" t="str">
-        <x:v>Yo-Chi Double Bay</x:v>
+        <x:v>Yo-Chi Eastland</x:v>
       </x:c>
       <x:c r="B25" s="7" t="str">
-        <x:v>NSW</x:v>
+        <x:v>VIC</x:v>
       </x:c>
       <x:c r="C25" s="7" t="str">
-        <x:v>2024-09-17</x:v>
+        <x:v>2025-08-11</x:v>
       </x:c>
       <x:c r="D25" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E25" s="7" t="str">
-        <x:v>Shop 16, Kiaora Place,</x:v>
+        <x:v>Tenancy 2053 (Lvl 2) – Eastland Shopping Centre</x:v>
       </x:c>
       <x:c r="F25" s="7" t="str">
-        <x:v>Double Bay</x:v>
+        <x:v>Ringwood</x:v>
       </x:c>
       <x:c r="G25" s="7" t="n">
-        <x:v>2028</x:v>
+        <x:v>3135</x:v>
       </x:c>
       <x:c r="H25" s="7" t="str">
-        <x:v>02 8338 7726</x:v>
+        <x:v>03 9018 9211</x:v>
       </x:c>
       <x:c r="I25" s="7" t="str">
-        <x:v>doublebay@yochi.com.au</x:v>
+        <x:v>eastland@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="7" t="str">
-        <x:v>Yo-Chi Eastland</x:v>
+        <x:v>Yo-Chi Forrest Chase</x:v>
       </x:c>
       <x:c r="B26" s="7" t="str">
-        <x:v>VIC</x:v>
+        <x:v>WA</x:v>
       </x:c>
       <x:c r="C26" s="7" t="str">
-        <x:v>2025-08-11</x:v>
+        <x:v>2024-12-01</x:v>
       </x:c>
       <x:c r="D26" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E26" s="7" t="str">
-        <x:v>Tenancy 2053 (Lvl 2) – Eastland Shopping Centre</x:v>
+        <x:v>Shop T06, Forrest Chase Shopping Centre, Murray Street</x:v>
       </x:c>
       <x:c r="F26" s="7" t="str">
-        <x:v>Ringwood</x:v>
+        <x:v>Perth</x:v>
       </x:c>
       <x:c r="G26" s="7" t="n">
-        <x:v>3135</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="H26" s="7" t="str">
-        <x:v>03 9018 9211</x:v>
+        <x:v>08 9446 8440</x:v>
       </x:c>
       <x:c r="I26" s="7" t="str">
-        <x:v>eastland@yochi.com.au</x:v>
+        <x:v>forrestchase@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="7" t="str">
-        <x:v>Yo-Chi Forrest Chase</x:v>
+        <x:v>Yo-Chi Fremantle</x:v>
       </x:c>
       <x:c r="B27" s="7" t="str">
         <x:v>WA</x:v>
       </x:c>
       <x:c r="C27" s="7" t="str">
-        <x:v>2024-12-01</x:v>
+        <x:v>2024-03-26</x:v>
       </x:c>
       <x:c r="D27" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E27" s="7" t="str">
-        <x:v>Shop T06, Forrest Chase Shopping Centre, Murray Street</x:v>
+        <x:v>5/36 South Terrace</x:v>
       </x:c>
       <x:c r="F27" s="7" t="str">
-        <x:v>Perth</x:v>
+        <x:v>Fremantle</x:v>
       </x:c>
       <x:c r="G27" s="7" t="n">
-        <x:v>6000</x:v>
+        <x:v>6160</x:v>
       </x:c>
       <x:c r="H27" s="7" t="str">
-        <x:v>08 9446 8440</x:v>
+        <x:v>08 6269 0003</x:v>
       </x:c>
       <x:c r="I27" s="7" t="str">
-        <x:v>forrestchase@yochi.com.au</x:v>
+        <x:v>fremantle@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="7" t="str">
-        <x:v>Yo-Chi Fremantle</x:v>
+        <x:v>Yo-Chi Gasworks</x:v>
       </x:c>
       <x:c r="B28" s="7" t="str">
-        <x:v>WA</x:v>
+        <x:v>QLD</x:v>
       </x:c>
       <x:c r="C28" s="7" t="str">
-        <x:v>2024-03-26</x:v>
+        <x:v>2024-08-27</x:v>
       </x:c>
       <x:c r="D28" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E28" s="7" t="str">
-        <x:v>5/36 South Terrace</x:v>
+        <x:v>Shop R00-10A, Gasworks Plaza,  76 Skyring Terrace</x:v>
       </x:c>
       <x:c r="F28" s="7" t="str">
-        <x:v>Fremantle</x:v>
+        <x:v>Newstead </x:v>
       </x:c>
       <x:c r="G28" s="7" t="n">
-        <x:v>6160</x:v>
+        <x:v>4006</x:v>
       </x:c>
       <x:c r="H28" s="7" t="str">
-        <x:v>08 6269 0003</x:v>
+        <x:v>07 3117 9466</x:v>
       </x:c>
       <x:c r="I28" s="7" t="str">
-        <x:v>fremantle@yochi.com.au</x:v>
+        <x:v>gasworks@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="7" t="str">
-        <x:v>Yo-Chi Gasworks</x:v>
+        <x:v>Yo-Chi George St</x:v>
       </x:c>
       <x:c r="B29" s="7" t="str">
-        <x:v>QLD</x:v>
+        <x:v>NSW</x:v>
       </x:c>
       <x:c r="C29" s="7" t="str">
-        <x:v>2024-08-27</x:v>
+        <x:v>2025-08-27</x:v>
       </x:c>
       <x:c r="D29" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E29" s="7" t="str">
-        <x:v>Shop R00-10A, Gasworks Plaza,  76 Skyring Terrace</x:v>
+        <x:v>614 George Street, Sydney NSW 2000</x:v>
       </x:c>
       <x:c r="F29" s="7" t="str">
-        <x:v>Newstead </x:v>
+        <x:v>Sydney</x:v>
       </x:c>
       <x:c r="G29" s="7" t="n">
-        <x:v>4006</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="H29" s="7" t="str">
-        <x:v>07 3117 9466</x:v>
+        <x:v>02 9870 0287</x:v>
       </x:c>
       <x:c r="I29" s="7" t="str">
-        <x:v>gasworks@yochi.com.au</x:v>
+        <x:v>georgest@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="7" t="str">
-        <x:v>Yo-Chi George St</x:v>
+        <x:v>Yo-Chi Glenelg</x:v>
       </x:c>
       <x:c r="B30" s="7" t="str">
-        <x:v>NSW</x:v>
+        <x:v>SA</x:v>
       </x:c>
       <x:c r="C30" s="7" t="str">
-        <x:v>2025-08-27</x:v>
+        <x:v>2021-10-08</x:v>
       </x:c>
       <x:c r="D30" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E30" s="7" t="str">
-        <x:v>614 George Street, Sydney NSW 2000</x:v>
+        <x:v>53 Jetty Rd</x:v>
       </x:c>
       <x:c r="F30" s="7" t="str">
-        <x:v>Sydney</x:v>
+        <x:v>Glenelg</x:v>
       </x:c>
       <x:c r="G30" s="7" t="n">
-        <x:v>2000</x:v>
+        <x:v>5045</x:v>
       </x:c>
       <x:c r="H30" s="7" t="str">
-        <x:v>02 9870 0287</x:v>
+        <x:v>08 8376 7956</x:v>
       </x:c>
       <x:c r="I30" s="7" t="str">
-        <x:v>georgest@yochi.com.au</x:v>
+        <x:v>glenelg@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="7" t="str">
-        <x:v>Yo-Chi Glenelg</x:v>
+        <x:v>Yo-Chi Gouger St</x:v>
       </x:c>
       <x:c r="B31" s="7" t="str">
         <x:v>SA</x:v>
       </x:c>
       <x:c r="C31" s="7" t="str">
-        <x:v>2021-10-08</x:v>
+        <x:v>2021-11-25</x:v>
       </x:c>
       <x:c r="D31" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E31" s="7" t="str">
-        <x:v>53 Jetty Rd</x:v>
+        <x:v>41 Gouger St</x:v>
       </x:c>
       <x:c r="F31" s="7" t="str">
-        <x:v>Glenelg</x:v>
+        <x:v>Adelaide</x:v>
       </x:c>
       <x:c r="G31" s="7" t="n">
-        <x:v>5045</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="H31" s="7" t="str">
-        <x:v>08 8376 7956</x:v>
+        <x:v>08 8221 5441</x:v>
       </x:c>
       <x:c r="I31" s="7" t="str">
-        <x:v>glenelg@yochi.com.au</x:v>
+        <x:v>gouger@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="7" t="str">
-        <x:v>Yo-Chi Gouger St</x:v>
+        <x:v>Yo-Chi Harbour Town</x:v>
       </x:c>
       <x:c r="B32" s="7" t="str">
-        <x:v>SA</x:v>
+        <x:v>QLD</x:v>
       </x:c>
       <x:c r="C32" s="7" t="str">
-        <x:v>2021-11-25</x:v>
+        <x:v>2026-04-11</x:v>
       </x:c>
       <x:c r="D32" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E32" s="7" t="str">
-        <x:v>41 Gouger St</x:v>
+        <x:v>B006 Yo Chi at Harbour Town Premium Outlets 147-189 Brisbane Road</x:v>
       </x:c>
       <x:c r="F32" s="7" t="str">
-        <x:v>Adelaide</x:v>
+        <x:v>Biggera Waters</x:v>
       </x:c>
       <x:c r="G32" s="7" t="n">
-        <x:v>5000</x:v>
+        <x:v>4216</x:v>
       </x:c>
       <x:c r="H32" s="7" t="str">
-        <x:v>08 8221 5441</x:v>
+        <x:v>07 5638 4241</x:v>
       </x:c>
       <x:c r="I32" s="7" t="str">
-        <x:v>gouger@yochi.com.au</x:v>
+        <x:v>harbourtown@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="7" t="str">
-        <x:v>Yo-Chi Harbour Town</x:v>
+        <x:v>Yo-Chi Hawthorn</x:v>
       </x:c>
       <x:c r="B33" s="7" t="str">
-        <x:v>QLD</x:v>
+        <x:v>VIC</x:v>
       </x:c>
       <x:c r="C33" s="7" t="str">
-        <x:v>2026-04-11</x:v>
+        <x:v>2014-12-15</x:v>
       </x:c>
       <x:c r="D33" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E33" s="7" t="str">
-        <x:v>B006 Yo Chi at Harbour Town Premium Outlets 147-189 Brisbane Road</x:v>
+        <x:v>673 Glenferrie Rd</x:v>
       </x:c>
       <x:c r="F33" s="7" t="str">
-        <x:v>Biggera Waters</x:v>
+        <x:v>Hawthorn</x:v>
       </x:c>
       <x:c r="G33" s="7" t="n">
-        <x:v>4216</x:v>
+        <x:v>3122</x:v>
       </x:c>
       <x:c r="H33" s="7" t="str">
-        <x:v>07 5638 4241</x:v>
+        <x:v>03 9819 0046</x:v>
       </x:c>
       <x:c r="I33" s="7" t="str">
-        <x:v>harbourtown@yochi.com.au</x:v>
+        <x:v>hawthorn@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="7" t="str">
-        <x:v>Yo-Chi Hawthorn</x:v>
+        <x:v>Yo-Chi Henley Beach</x:v>
       </x:c>
       <x:c r="B34" s="7" t="str">
-        <x:v>VIC</x:v>
+        <x:v>SA</x:v>
       </x:c>
       <x:c r="C34" s="7" t="str">
-        <x:v>2014-12-15</x:v>
+        <x:v>2023-07-10</x:v>
       </x:c>
       <x:c r="D34" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E34" s="7" t="str">
-        <x:v>673 Glenferrie Rd</x:v>
+        <x:v>22/330 Seaview Rd</x:v>
       </x:c>
       <x:c r="F34" s="7" t="str">
-        <x:v>Hawthorn</x:v>
+        <x:v>Henley Beach</x:v>
       </x:c>
       <x:c r="G34" s="7" t="n">
-        <x:v>3122</x:v>
+        <x:v>5022</x:v>
       </x:c>
       <x:c r="H34" s="7" t="str">
-        <x:v>03 9819 0046</x:v>
+        <x:v>08 8332 9406</x:v>
       </x:c>
       <x:c r="I34" s="7" t="str">
-        <x:v>hawthorn@yochi.com.au</x:v>
+        <x:v>henley@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="7" t="str">
-        <x:v>Yo-Chi Henley Beach</x:v>
+        <x:v>Yo-Chi Highgate</x:v>
       </x:c>
       <x:c r="B35" s="7" t="str">
-        <x:v>SA</x:v>
+        <x:v>WA</x:v>
       </x:c>
       <x:c r="C35" s="7" t="str">
-        <x:v>2023-07-10</x:v>
+        <x:v>2024-05-09</x:v>
       </x:c>
       <x:c r="D35" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E35" s="7" t="str">
-        <x:v>22/330 Seaview Rd</x:v>
+        <x:v>35-36/ 500 Beaufort Street</x:v>
       </x:c>
       <x:c r="F35" s="7" t="str">
-        <x:v>Henley Beach</x:v>
+        <x:v>Highgate</x:v>
       </x:c>
       <x:c r="G35" s="7" t="n">
-        <x:v>5022</x:v>
+        <x:v>6003</x:v>
       </x:c>
       <x:c r="H35" s="7" t="str">
-        <x:v>08 8332 9406</x:v>
+        <x:v>08 6364 0660</x:v>
       </x:c>
       <x:c r="I35" s="7" t="str">
-        <x:v>henley@yochi.com.au</x:v>
+        <x:v>highgate@yochi.com</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="7" t="str">
-        <x:v>Yo-Chi Highgate</x:v>
+        <x:v>Yo-Chi Highpoint</x:v>
       </x:c>
       <x:c r="B36" s="7" t="str">
-        <x:v>WA</x:v>
+        <x:v>VIC</x:v>
       </x:c>
       <x:c r="C36" s="7" t="str">
-        <x:v>2024-05-09</x:v>
+        <x:v>2025-07-14</x:v>
       </x:c>
       <x:c r="D36" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E36" s="7" t="str">
-        <x:v>35-36/ 500 Beaufort Street</x:v>
+        <x:v>Tenancy 1133, 120-200 Rosamond Rd</x:v>
       </x:c>
       <x:c r="F36" s="7" t="str">
-        <x:v>Highgate</x:v>
+        <x:v>Maribrynong</x:v>
       </x:c>
       <x:c r="G36" s="7" t="n">
-        <x:v>6003</x:v>
+        <x:v>3032</x:v>
       </x:c>
       <x:c r="H36" s="7" t="str">
-        <x:v>08 6364 0660</x:v>
+        <x:v>03 9002 1158</x:v>
       </x:c>
       <x:c r="I36" s="7" t="str">
-        <x:v>highgate@yochi.com</x:v>
+        <x:v>highpoint@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="7" t="str">
-        <x:v>Yo-Chi Highpoint</x:v>
+        <x:v>Yo-Chi Indooroopilly</x:v>
       </x:c>
       <x:c r="B37" s="7" t="str">
-        <x:v>VIC</x:v>
+        <x:v>QLD</x:v>
       </x:c>
       <x:c r="C37" s="7" t="str">
-        <x:v>2025-07-14</x:v>
+        <x:v>2026-03-07</x:v>
       </x:c>
       <x:c r="D37" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E37" s="7" t="str">
-        <x:v>Tenancy 1133, 120-200 Rosamond Rd</x:v>
+        <x:v>R03-039 Indooroopilly Shopping Centre, 322 Moggill Road</x:v>
       </x:c>
       <x:c r="F37" s="7" t="str">
-        <x:v>Maribrynong</x:v>
+        <x:v>Indooroopilly</x:v>
       </x:c>
       <x:c r="G37" s="7" t="n">
-        <x:v>3032</x:v>
+        <x:v>4068</x:v>
       </x:c>
       <x:c r="H37" s="7" t="str">
-        <x:v>03 9002 1158</x:v>
+        <x:v>07 3525 2184</x:v>
       </x:c>
       <x:c r="I37" s="7" t="str">
-        <x:v>highpoint@yochi.com.au</x:v>
+        <x:v>indooroopilly@yochhi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="7" t="str">
-        <x:v>Yo-Chi Indooroopilly</x:v>
+        <x:v>Yo-Chi Karrinyup</x:v>
       </x:c>
       <x:c r="B38" s="7" t="str">
-        <x:v>QLD</x:v>
+        <x:v>WA</x:v>
       </x:c>
       <x:c r="C38" s="7" t="str">
-        <x:v>2026-03-07</x:v>
+        <x:v>2023-10-06</x:v>
       </x:c>
       <x:c r="D38" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E38" s="7" t="str">
-        <x:v>R03-039 Indooroopilly Shopping Centre, 322 Moggill Road</x:v>
+        <x:v>FC0212 Karrinyup Shopping Centre,  200 Karrinyup Road</x:v>
       </x:c>
       <x:c r="F38" s="7" t="str">
-        <x:v>Indooroopilly</x:v>
+        <x:v>Karrinyup</x:v>
       </x:c>
       <x:c r="G38" s="7" t="n">
-        <x:v>4068</x:v>
+        <x:v>6018</x:v>
       </x:c>
       <x:c r="H38" s="7" t="str">
-        <x:v>07 3525 2184</x:v>
+        <x:v>08 6556 0390</x:v>
       </x:c>
       <x:c r="I38" s="7" t="str">
-        <x:v>indooroopilly@yochhi.com.au</x:v>
+        <x:v>karrinyup@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="7" t="str">
-        <x:v>Yo-Chi Karrinyup</x:v>
+        <x:v>Yo-Chi Kawana Waters</x:v>
       </x:c>
       <x:c r="B39" s="7" t="str">
-        <x:v>WA</x:v>
+        <x:v>QLD</x:v>
       </x:c>
       <x:c r="C39" s="7" t="str">
-        <x:v>2023-10-06</x:v>
+        <x:v>2026-03-14</x:v>
       </x:c>
       <x:c r="D39" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E39" s="7" t="str">
-        <x:v>FC0212 Karrinyup Shopping Centre,  200 Karrinyup Road</x:v>
+        <x:v>Shop 405, Kawana Shoppingworld, 119 Point Cartwright Dr,</x:v>
       </x:c>
       <x:c r="F39" s="7" t="str">
-        <x:v>Karrinyup</x:v>
+        <x:v>Buddina</x:v>
       </x:c>
       <x:c r="G39" s="7" t="n">
-        <x:v>6018</x:v>
+        <x:v>4575</x:v>
       </x:c>
       <x:c r="H39" s="7" t="str">
-        <x:v>08 6556 0390</x:v>
+        <x:v>07 5293 7869</x:v>
       </x:c>
       <x:c r="I39" s="7" t="str">
-        <x:v>karrinyup@yochi.com.au</x:v>
+        <x:v>kawana@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="7" t="str">
-        <x:v>Yo-Chi Kawana Waters</x:v>
+        <x:v>Yo-Chi Lane Cove</x:v>
       </x:c>
       <x:c r="B40" s="7" t="str">
-        <x:v>QLD</x:v>
+        <x:v>NSW</x:v>
       </x:c>
       <x:c r="C40" s="7" t="str">
-        <x:v>2026-03-14</x:v>
+        <x:v>2023-07-04</x:v>
       </x:c>
       <x:c r="D40" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E40" s="7" t="str">
-        <x:v>Shop 405, Kawana Shoppingworld, 119 Point Cartwright Dr,</x:v>
+        <x:v>T15 &amp; T16,  24-28 Burns Bay Road</x:v>
       </x:c>
       <x:c r="F40" s="7" t="str">
-        <x:v>Buddina</x:v>
+        <x:v>Lane Cove</x:v>
       </x:c>
       <x:c r="G40" s="7" t="n">
-        <x:v>4575</x:v>
+        <x:v>2066</x:v>
       </x:c>
       <x:c r="H40" s="7" t="str">
-        <x:v>07 5293 7869</x:v>
+        <x:v>02 8205 7911</x:v>
       </x:c>
       <x:c r="I40" s="7" t="str">
-        <x:v>kawana@yochi.com.au</x:v>
+        <x:v>lanecove@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="7" t="str">
-        <x:v>Yo-Chi Lane Cove</x:v>
+        <x:v>Yo-Chi Leederville</x:v>
       </x:c>
       <x:c r="B41" s="7" t="str">
-        <x:v>NSW</x:v>
+        <x:v>WA</x:v>
       </x:c>
       <x:c r="C41" s="7" t="str">
-        <x:v>2023-07-04</x:v>
+        <x:v>2023-12-12</x:v>
       </x:c>
       <x:c r="D41" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E41" s="7" t="str">
-        <x:v>T15 &amp; T16,  24-28 Burns Bay Road</x:v>
+        <x:v>149 Oxford St </x:v>
       </x:c>
       <x:c r="F41" s="7" t="str">
-        <x:v>Lane Cove</x:v>
+        <x:v>Leederville</x:v>
       </x:c>
       <x:c r="G41" s="7" t="n">
-        <x:v>2066</x:v>
+        <x:v>6007</x:v>
       </x:c>
       <x:c r="H41" s="7" t="str">
-        <x:v>02 8205 7911</x:v>
+        <x:v>08 6263 4188</x:v>
       </x:c>
       <x:c r="I41" s="7" t="str">
-        <x:v>lanecove@yochi.com.au</x:v>
+        <x:v>leederville@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="7" t="str">
-        <x:v>Yo-Chi Leederville</x:v>
+        <x:v>Yo-Chi Macquarie</x:v>
       </x:c>
       <x:c r="B42" s="7" t="str">
-        <x:v>WA</x:v>
+        <x:v>NSW</x:v>
       </x:c>
       <x:c r="C42" s="7" t="str">
-        <x:v>2023-12-12</x:v>
+        <x:v>2023-03-04</x:v>
       </x:c>
       <x:c r="D42" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E42" s="7" t="str">
-        <x:v>149 Oxford St </x:v>
+        <x:v> Shop No. 3404 Level Three Macquarie Centre</x:v>
       </x:c>
       <x:c r="F42" s="7" t="str">
-        <x:v>Leederville</x:v>
+        <x:v>Cnr Waterloo Rd</x:v>
       </x:c>
       <x:c r="G42" s="7" t="n">
-        <x:v>6007</x:v>
+        <x:v>2113</x:v>
       </x:c>
       <x:c r="H42" s="7" t="str">
-        <x:v>08 6263 4188</x:v>
+        <x:v>02 9194 4464</x:v>
       </x:c>
       <x:c r="I42" s="7" t="str">
-        <x:v>leederville@yochi.com.au</x:v>
+        <x:v>macquarie@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="7" t="str">
-        <x:v>Yo-Chi Macquarie</x:v>
+        <x:v>Yo-Chi Malvern</x:v>
       </x:c>
       <x:c r="B43" s="7" t="str">
-        <x:v>NSW</x:v>
+        <x:v>VIC</x:v>
       </x:c>
       <x:c r="C43" s="7" t="str">
-        <x:v>2023-03-04</x:v>
+        <x:v>2023-09-13</x:v>
       </x:c>
       <x:c r="D43" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E43" s="7" t="str">
-        <x:v> Shop No. 3404 Level Three Macquarie Centre</x:v>
+        <x:v>212 Glenferrie Rd</x:v>
       </x:c>
       <x:c r="F43" s="7" t="str">
-        <x:v>Cnr Waterloo Rd</x:v>
+        <x:v>Malvern</x:v>
       </x:c>
       <x:c r="G43" s="7" t="n">
-        <x:v>2113</x:v>
+        <x:v>3144</x:v>
       </x:c>
       <x:c r="H43" s="7" t="str">
-        <x:v>02 9194 4464</x:v>
+        <x:v>0 9500 2637</x:v>
       </x:c>
       <x:c r="I43" s="7" t="str">
-        <x:v>macquarie@yochi.com.au</x:v>
+        <x:v>malvern@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="7" t="str">
-        <x:v>Yo-Chi Malvern</x:v>
+        <x:v>Yo-Chi Mandurah</x:v>
       </x:c>
       <x:c r="B44" s="7" t="str">
-        <x:v>VIC</x:v>
+        <x:v>WA</x:v>
       </x:c>
       <x:c r="C44" s="7" t="str">
-        <x:v>2023-09-13</x:v>
+        <x:v>2024-04-22</x:v>
       </x:c>
       <x:c r="D44" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E44" s="7" t="str">
-        <x:v>212 Glenferrie Rd</x:v>
+        <x:v>Shop 6,  14-16 Mandurah Terrace</x:v>
       </x:c>
       <x:c r="F44" s="7" t="str">
-        <x:v>Malvern</x:v>
+        <x:v>Mandurah</x:v>
       </x:c>
       <x:c r="G44" s="7" t="n">
-        <x:v>3144</x:v>
+        <x:v>6210</x:v>
       </x:c>
       <x:c r="H44" s="7" t="str">
-        <x:v>0 9500 2637</x:v>
+        <x:v>08 9511 1020</x:v>
       </x:c>
       <x:c r="I44" s="7" t="str">
-        <x:v>malvern@yochi.com.au</x:v>
+        <x:v>mandurah@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="7" t="str">
-        <x:v>Yo-Chi Mandurah</x:v>
+        <x:v>Yo-Chi Manly</x:v>
       </x:c>
       <x:c r="B45" s="7" t="str">
-        <x:v>WA</x:v>
+        <x:v>NSW</x:v>
       </x:c>
       <x:c r="C45" s="7" t="str">
-        <x:v>2024-04-22</x:v>
+        <x:v>2023-12-11</x:v>
       </x:c>
       <x:c r="D45" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E45" s="7" t="str">
-        <x:v>Shop 6,  14-16 Mandurah Terrace</x:v>
+        <x:v>68 The Corso</x:v>
       </x:c>
       <x:c r="F45" s="7" t="str">
-        <x:v>Mandurah</x:v>
+        <x:v>Manly</x:v>
       </x:c>
       <x:c r="G45" s="7" t="n">
-        <x:v>6210</x:v>
+        <x:v>2095</x:v>
       </x:c>
       <x:c r="H45" s="7" t="str">
-        <x:v>08 9511 1020</x:v>
+        <x:v>02 9909 6003</x:v>
       </x:c>
       <x:c r="I45" s="7" t="str">
-        <x:v>mandurah@yochi.com.au</x:v>
+        <x:v>manly@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="7" t="str">
-        <x:v>Yo-Chi Manly</x:v>
+        <x:v>Yo-Chi Mt Gravatt</x:v>
       </x:c>
       <x:c r="B46" s="7" t="str">
-        <x:v>NSW</x:v>
+        <x:v>QLD </x:v>
       </x:c>
       <x:c r="C46" s="7" t="str">
-        <x:v>2023-12-11</x:v>
+        <x:v>2023-05-28</x:v>
       </x:c>
       <x:c r="D46" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E46" s="7" t="str">
-        <x:v>68 The Corso</x:v>
+        <x:v>Restaurant R5 Westfield Mt Gravatt,  Kessels Rd</x:v>
       </x:c>
       <x:c r="F46" s="7" t="str">
-        <x:v>Manly</x:v>
+        <x:v>Upper Mount Gravatt</x:v>
       </x:c>
       <x:c r="G46" s="7" t="n">
-        <x:v>2095</x:v>
+        <x:v>4122</x:v>
       </x:c>
       <x:c r="H46" s="7" t="str">
-        <x:v>02 9909 6003</x:v>
+        <x:v> 07 3114 2687</x:v>
       </x:c>
       <x:c r="I46" s="7" t="str">
-        <x:v>manly@yochi.com.au</x:v>
+        <x:v>mountgravatt@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="7" t="str">
-        <x:v>Yo-Chi Mt Gravatt</x:v>
+        <x:v>Yo-Chi Newtown</x:v>
       </x:c>
       <x:c r="B47" s="7" t="str">
-        <x:v>QLD </x:v>
+        <x:v>NSW</x:v>
       </x:c>
       <x:c r="C47" s="7" t="str">
-        <x:v>2023-05-28</x:v>
+        <x:v>2023-05-07</x:v>
       </x:c>
       <x:c r="D47" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E47" s="7" t="str">
-        <x:v>Restaurant R5 Westfield Mt Gravatt,  Kessels Rd</x:v>
+        <x:v>293 King Street</x:v>
       </x:c>
       <x:c r="F47" s="7" t="str">
-        <x:v>Upper Mount Gravatt</x:v>
+        <x:v>Newtown</x:v>
       </x:c>
       <x:c r="G47" s="7" t="n">
-        <x:v>4122</x:v>
+        <x:v>2042</x:v>
       </x:c>
       <x:c r="H47" s="7" t="str">
-        <x:v> 07 3114 2687</x:v>
+        <x:v>02 8218 2414</x:v>
       </x:c>
       <x:c r="I47" s="7" t="str">
-        <x:v>mountgravatt@yochi.com.au</x:v>
+        <x:v>newtown@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="7" t="str">
-        <x:v>Yo-Chi Newtown</x:v>
+        <x:v>Yo-Chi Noosa</x:v>
       </x:c>
       <x:c r="B48" s="7" t="str">
-        <x:v>NSW</x:v>
+        <x:v>QLD</x:v>
       </x:c>
       <x:c r="C48" s="7" t="str">
-        <x:v>2023-05-07</x:v>
+        <x:v>2022-07-19</x:v>
       </x:c>
       <x:c r="D48" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E48" s="7" t="str">
-        <x:v>293 King Street</x:v>
+        <x:v>Unit 5/30 Hastings St</x:v>
       </x:c>
       <x:c r="F48" s="7" t="str">
-        <x:v>Newtown</x:v>
+        <x:v>Noosa Heads</x:v>
       </x:c>
       <x:c r="G48" s="7" t="n">
-        <x:v>2042</x:v>
+        <x:v>4567</x:v>
       </x:c>
       <x:c r="H48" s="7" t="str">
-        <x:v>02 8218 2414</x:v>
+        <x:v>07 5343 1873</x:v>
       </x:c>
       <x:c r="I48" s="7" t="str">
-        <x:v>newtown@yochi.com.au</x:v>
+        <x:v>noosa@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="7" t="str">
-        <x:v>Yo-Chi Noosa</x:v>
+        <x:v>Yo-Chi Norwood</x:v>
       </x:c>
       <x:c r="B49" s="7" t="str">
-        <x:v>QLD</x:v>
+        <x:v>SA</x:v>
       </x:c>
       <x:c r="C49" s="7" t="str">
-        <x:v>2022-07-19</x:v>
+        <x:v>2021-03-06</x:v>
       </x:c>
       <x:c r="D49" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E49" s="7" t="str">
-        <x:v>Unit 5/30 Hastings St</x:v>
+        <x:v>171a The Parade</x:v>
       </x:c>
       <x:c r="F49" s="7" t="str">
-        <x:v>Noosa Heads</x:v>
+        <x:v>Norwood</x:v>
       </x:c>
       <x:c r="G49" s="7" t="n">
-        <x:v>4567</x:v>
+        <x:v>5067</x:v>
       </x:c>
       <x:c r="H49" s="7" t="str">
-        <x:v>07 5343 1873</x:v>
+        <x:v>08 8331 2534</x:v>
       </x:c>
       <x:c r="I49" s="7" t="str">
-        <x:v>noosa@yochi.com.au</x:v>
+        <x:v>norwood@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="7" t="str">
-        <x:v>Yo-Chi Norwood</x:v>
+        <x:v>Yo-Chi Paddington</x:v>
       </x:c>
       <x:c r="B50" s="7" t="str">
-        <x:v>SA</x:v>
+        <x:v>QLD</x:v>
       </x:c>
       <x:c r="C50" s="7" t="str">
-        <x:v>2021-03-06</x:v>
+        <x:v>2023-11-13</x:v>
       </x:c>
       <x:c r="D50" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E50" s="7" t="str">
-        <x:v>171a The Parade</x:v>
+        <x:v>Shop 5,  155 Baroona Road</x:v>
       </x:c>
       <x:c r="F50" s="7" t="str">
-        <x:v>Norwood</x:v>
+        <x:v>Paddington</x:v>
       </x:c>
       <x:c r="G50" s="7" t="n">
-        <x:v>5067</x:v>
+        <x:v>4064</x:v>
       </x:c>
       <x:c r="H50" s="7" t="str">
-        <x:v>08 8331 2534</x:v>
+        <x:v>07 3152 6229</x:v>
       </x:c>
       <x:c r="I50" s="7" t="str">
-        <x:v>norwood@yochi.com.au</x:v>
+        <x:v>paddington@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="7" t="str">
-        <x:v>Yo-Chi Paddington</x:v>
+        <x:v>Yo-Chi Penrith</x:v>
       </x:c>
       <x:c r="B51" s="7" t="str">
-        <x:v>QLD</x:v>
+        <x:v>NSW</x:v>
       </x:c>
       <x:c r="C51" s="7" t="str">
-        <x:v>2023-11-13</x:v>
+        <x:v>2024-11-18</x:v>
       </x:c>
       <x:c r="D51" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E51" s="7" t="str">
-        <x:v>Shop 5,  155 Baroona Road</x:v>
+        <x:v>Shop 53, Westfield Penrith, 585 High St</x:v>
       </x:c>
       <x:c r="F51" s="7" t="str">
-        <x:v>Paddington</x:v>
+        <x:v>Penrith</x:v>
       </x:c>
       <x:c r="G51" s="7" t="n">
-        <x:v>4064</x:v>
+        <x:v>2750</x:v>
       </x:c>
       <x:c r="H51" s="7" t="str">
-        <x:v>07 3152 6229</x:v>
+        <x:v>02 4744 2074</x:v>
       </x:c>
       <x:c r="I51" s="7" t="str">
-        <x:v>paddington@yochi.com.au</x:v>
+        <x:v>penrith@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="7" t="str">
-        <x:v>Yo-Chi Penrith</x:v>
+        <x:v>Yo-Chi Prospect</x:v>
       </x:c>
       <x:c r="B52" s="7" t="str">
-        <x:v>NSW</x:v>
+        <x:v>SA</x:v>
       </x:c>
       <x:c r="C52" s="7" t="str">
-        <x:v>2024-11-18</x:v>
+        <x:v>2025-07-01</x:v>
       </x:c>
       <x:c r="D52" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E52" s="7" t="str">
-        <x:v>Shop 53, Westfield Penrith, 585 High St</x:v>
+        <x:v>T6 69-73 Prospect Rd</x:v>
       </x:c>
       <x:c r="F52" s="7" t="str">
-        <x:v>Penrith</x:v>
+        <x:v>Prospect</x:v>
       </x:c>
       <x:c r="G52" s="7" t="n">
-        <x:v>2750</x:v>
+        <x:v>5082</x:v>
       </x:c>
       <x:c r="H52" s="7" t="str">
-        <x:v>02 4744 2074</x:v>
+        <x:v>08 8464 0644</x:v>
       </x:c>
       <x:c r="I52" s="7" t="str">
-        <x:v>penrith@yochi.com.au</x:v>
+        <x:v>prospect@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="7" t="str">
-        <x:v>Yo-Chi Prospect</x:v>
+        <x:v>Yo-Chi QV</x:v>
       </x:c>
       <x:c r="B53" s="7" t="str">
-        <x:v>SA</x:v>
+        <x:v>VIC</x:v>
       </x:c>
       <x:c r="C53" s="7" t="str">
-        <x:v>2025-07-01</x:v>
+        <x:v>2025-11-29</x:v>
       </x:c>
       <x:c r="D53" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E53" s="7" t="str">
-        <x:v>T6 69-73 Prospect Rd</x:v>
+        <x:v>QV Melbourne Corner Lonsdale St &amp; Swanston St </x:v>
       </x:c>
       <x:c r="F53" s="7" t="str">
-        <x:v>Prospect</x:v>
+        <x:v>Melbourne</x:v>
       </x:c>
       <x:c r="G53" s="7" t="n">
-        <x:v>5082</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="H53" s="7" t="str">
-        <x:v>08 8464 0644</x:v>
+        <x:v>03 9116 3787</x:v>
       </x:c>
       <x:c r="I53" s="7" t="str">
-        <x:v>prospect@yochi.com.au</x:v>
+        <x:v>qv@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="7" t="str">
-        <x:v>Yo-Chi QV</x:v>
+        <x:v>Yo-Chi Randwick</x:v>
       </x:c>
       <x:c r="B54" s="7" t="str">
-        <x:v>VIC</x:v>
+        <x:v>NSW</x:v>
       </x:c>
       <x:c r="C54" s="7" t="str">
         <x:v>2025-11-29</x:v>
@@ -1796,482 +1806,453 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E54" s="7" t="str">
-        <x:v>QV Melbourne Corner Lonsdale St &amp; Swanston St </x:v>
+        <x:v>73 Belmore Rd, Randwick NSW 2031</x:v>
       </x:c>
       <x:c r="F54" s="7" t="str">
-        <x:v>Melbourne</x:v>
+        <x:v>Randwick</x:v>
       </x:c>
       <x:c r="G54" s="7" t="n">
-        <x:v>3000</x:v>
+        <x:v>2031</x:v>
       </x:c>
       <x:c r="H54" s="7" t="str">
-        <x:v>03 9116 3787</x:v>
+        <x:v>02 8089 0396</x:v>
       </x:c>
       <x:c r="I54" s="7" t="str">
-        <x:v>qv@yochi.com.au</x:v>
+        <x:v>randwick@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="7" t="str">
-        <x:v>Yo-Chi Randwick</x:v>
+        <x:v>Yo-Chi Robina</x:v>
       </x:c>
       <x:c r="B55" s="7" t="str">
-        <x:v>NSW</x:v>
+        <x:v>QLD</x:v>
       </x:c>
       <x:c r="C55" s="7" t="str">
-        <x:v>2025-11-29</x:v>
+        <x:v>2024-06-19</x:v>
       </x:c>
       <x:c r="D55" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E55" s="7" t="str">
-        <x:v>73 Belmore Rd, Randwick NSW 2031</x:v>
+        <x:v>Shop 1009,  19  Robina Town Centre Drive</x:v>
       </x:c>
       <x:c r="F55" s="7" t="str">
-        <x:v>Randwick</x:v>
+        <x:v>Robina</x:v>
       </x:c>
       <x:c r="G55" s="7" t="n">
-        <x:v>2031</x:v>
+        <x:v>4226</x:v>
       </x:c>
       <x:c r="H55" s="7" t="str">
-        <x:v>02 8089 0396</x:v>
+        <x:v>07 5555 0177</x:v>
       </x:c>
       <x:c r="I55" s="7" t="str">
-        <x:v>randwick@yochi.com.au</x:v>
+        <x:v>robina@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="7" t="str">
-        <x:v>Yo-Chi Robina</x:v>
+        <x:v>Yo-Chi Rouse Hill</x:v>
       </x:c>
       <x:c r="B56" s="7" t="str">
-        <x:v>QLD</x:v>
+        <x:v>NSW</x:v>
       </x:c>
       <x:c r="C56" s="7" t="str">
-        <x:v>2024-06-19</x:v>
+        <x:v>2025-11-22</x:v>
       </x:c>
       <x:c r="D56" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E56" s="7" t="str">
-        <x:v>Shop 1009,  19  Robina Town Centre Drive</x:v>
+        <x:v>110, Rouse Hill Town Centre, Crn Windsor Road White Hart</x:v>
       </x:c>
       <x:c r="F56" s="7" t="str">
-        <x:v>Robina</x:v>
+        <x:v>Rouse Hill</x:v>
       </x:c>
       <x:c r="G56" s="7" t="n">
-        <x:v>4226</x:v>
+        <x:v>2155</x:v>
       </x:c>
       <x:c r="H56" s="7" t="str">
-        <x:v>07 5555 0177</x:v>
+        <x:v>02 8089 0397</x:v>
       </x:c>
       <x:c r="I56" s="7" t="str">
-        <x:v>robina@yochi.com.au</x:v>
+        <x:v>rousehill@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="7" t="str">
-        <x:v>Yo-Chi Rouse Hill</x:v>
+        <x:v>Yo-Chi Semaphore</x:v>
       </x:c>
       <x:c r="B57" s="7" t="str">
-        <x:v>NSW</x:v>
+        <x:v>SA</x:v>
       </x:c>
       <x:c r="C57" s="7" t="str">
-        <x:v>2025-11-22</x:v>
+        <x:v>2024-06-06</x:v>
       </x:c>
       <x:c r="D57" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E57" s="7" t="str">
-        <x:v>110, Rouse Hill Town Centre, Crn Windsor Road White Hart</x:v>
+        <x:v>Tenancy 1 &amp; 2,  24 Semaphore Road</x:v>
       </x:c>
       <x:c r="F57" s="7" t="str">
-        <x:v>Rouse Hill</x:v>
+        <x:v>Semaphore</x:v>
       </x:c>
       <x:c r="G57" s="7" t="n">
-        <x:v>2155</x:v>
+        <x:v>5019</x:v>
       </x:c>
       <x:c r="H57" s="7" t="str">
-        <x:v>02 8089 0397</x:v>
+        <x:v>08 8312 4666</x:v>
       </x:c>
       <x:c r="I57" s="7" t="str">
-        <x:v>rousehill@yochi.com.au</x:v>
+        <x:v>semaphore@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="7" t="str">
-        <x:v>Yo-Chi Semaphore</x:v>
+        <x:v>Yo-Chi South Perth</x:v>
       </x:c>
       <x:c r="B58" s="7" t="str">
-        <x:v>SA</x:v>
+        <x:v>WA</x:v>
       </x:c>
       <x:c r="C58" s="7" t="str">
-        <x:v>2024-06-06</x:v>
+        <x:v>2025-03-06</x:v>
       </x:c>
       <x:c r="D58" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E58" s="7" t="str">
-        <x:v>Tenancy 1 &amp; 2,  24 Semaphore Road</x:v>
+        <x:v>Shop 36 South Shore Centre, 85 South Perth Esplanade</x:v>
       </x:c>
       <x:c r="F58" s="7" t="str">
-        <x:v>Semaphore</x:v>
+        <x:v>South Perth</x:v>
       </x:c>
       <x:c r="G58" s="7" t="n">
-        <x:v>5019</x:v>
+        <x:v>6151</x:v>
       </x:c>
       <x:c r="H58" s="7" t="str">
-        <x:v>08 8312 4666</x:v>
+        <x:v>08 6363 5507</x:v>
       </x:c>
       <x:c r="I58" s="7" t="str">
-        <x:v>semaphore@yochi.com.au</x:v>
+        <x:v>southperth@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="7" t="str">
-        <x:v>Yo-Chi South Perth</x:v>
+        <x:v>Yo-Chi Southbank</x:v>
       </x:c>
       <x:c r="B59" s="7" t="str">
-        <x:v>WA</x:v>
+        <x:v>QLD</x:v>
       </x:c>
       <x:c r="C59" s="7" t="str">
-        <x:v>2025-03-06</x:v>
+        <x:v>2026-02-28</x:v>
       </x:c>
       <x:c r="D59" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E59" s="7" t="str">
-        <x:v>Shop 36 South Shore Centre, 85 South Perth Esplanade</x:v>
+        <x:v>Tenancy 1 / 167 Grey Street, South Brisbane, QLD, 4101</x:v>
       </x:c>
       <x:c r="F59" s="7" t="str">
-        <x:v>South Perth</x:v>
+        <x:v>South Brisbane</x:v>
       </x:c>
       <x:c r="G59" s="7" t="n">
-        <x:v>6151</x:v>
+        <x:v>4101</x:v>
       </x:c>
       <x:c r="H59" s="7" t="str">
-        <x:v>08 6363 5507</x:v>
+        <x:v>07 3525 2183</x:v>
       </x:c>
       <x:c r="I59" s="7" t="str">
-        <x:v>southperth@yochi.com.au</x:v>
+        <x:v>southbank@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="7" t="str">
-        <x:v>Yo-Chi Southbank</x:v>
+        <x:v>Yo-Chi Southland</x:v>
       </x:c>
       <x:c r="B60" s="7" t="str">
-        <x:v>QLD</x:v>
+        <x:v>VIC</x:v>
       </x:c>
       <x:c r="C60" s="7" t="str">
-        <x:v>2026-02-28</x:v>
+        <x:v>2025-06-21</x:v>
       </x:c>
       <x:c r="D60" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E60" s="7" t="str">
-        <x:v>Tenancy 1 / 167 Grey Street, South Brisbane, QLD, 4101</x:v>
+        <x:v>Shop 2090 A, 1239-1241 Nepean Highway</x:v>
       </x:c>
       <x:c r="F60" s="7" t="str">
-        <x:v>South Brisbane</x:v>
+        <x:v>Cheltenham</x:v>
       </x:c>
       <x:c r="G60" s="7" t="n">
-        <x:v>4101</x:v>
+        <x:v>3192</x:v>
       </x:c>
       <x:c r="H60" s="7" t="str">
-        <x:v>07 3525 2183</x:v>
+        <x:v>03 9017 5644</x:v>
       </x:c>
       <x:c r="I60" s="7" t="str">
-        <x:v>southbank@yochi.com.au</x:v>
+        <x:v>southland@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="7" t="str">
-        <x:v>Yo-Chi Southland</x:v>
+        <x:v>Yo-Chi Sunshine Plaza</x:v>
       </x:c>
       <x:c r="B61" s="7" t="str">
-        <x:v>VIC</x:v>
+        <x:v>QLD</x:v>
       </x:c>
       <x:c r="C61" s="7" t="str">
-        <x:v>2025-06-21</x:v>
+        <x:v>2023-04-30</x:v>
       </x:c>
       <x:c r="D61" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E61" s="7" t="str">
-        <x:v>Shop 2090 A, 1239-1241 Nepean Highway</x:v>
+        <x:v>Sunshine Plaza, Shop no. GD212, 154-164 Horton Parade</x:v>
       </x:c>
       <x:c r="F61" s="7" t="str">
-        <x:v>Cheltenham</x:v>
+        <x:v>Maroochydore</x:v>
       </x:c>
       <x:c r="G61" s="7" t="n">
-        <x:v>3192</x:v>
+        <x:v>4558</x:v>
       </x:c>
       <x:c r="H61" s="7" t="str">
-        <x:v>03 9017 5644</x:v>
+        <x:v>07 5334 1220</x:v>
       </x:c>
       <x:c r="I61" s="7" t="str">
-        <x:v>southland@yochi.com.au</x:v>
+        <x:v>sunshineplaza@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="7" t="str">
-        <x:v>Yo-Chi Sunshine Plaza</x:v>
+        <x:v>Yo-Chi Surry Hills</x:v>
       </x:c>
       <x:c r="B62" s="7" t="str">
-        <x:v>QLD</x:v>
+        <x:v>NSW</x:v>
       </x:c>
       <x:c r="C62" s="7" t="str">
-        <x:v>2023-04-30</x:v>
+        <x:v>2021-11-03</x:v>
       </x:c>
       <x:c r="D62" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E62" s="7" t="str">
-        <x:v>Sunshine Plaza, Shop no. GD212, 154-164 Horton Parade</x:v>
+        <x:v>435 Crown St</x:v>
       </x:c>
       <x:c r="F62" s="7" t="str">
-        <x:v>Maroochydore</x:v>
+        <x:v>Surry Hills</x:v>
       </x:c>
       <x:c r="G62" s="7" t="n">
-        <x:v>4558</x:v>
+        <x:v>2010</x:v>
       </x:c>
       <x:c r="H62" s="7" t="str">
-        <x:v>07 5334 1220</x:v>
+        <x:v>02 9319 7525</x:v>
       </x:c>
       <x:c r="I62" s="7" t="str">
-        <x:v>sunshineplaza@yochi.com.au</x:v>
+        <x:v>surryhills@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="7" t="str">
-        <x:v>Yo-Chi Surry Hills</x:v>
+        <x:v>Yo-Chi Tea Tree Plaza</x:v>
       </x:c>
       <x:c r="B63" s="7" t="str">
-        <x:v>NSW</x:v>
+        <x:v>SA</x:v>
       </x:c>
       <x:c r="C63" s="7" t="str">
-        <x:v>2021-11-03</x:v>
+        <x:v>2024-09-07</x:v>
       </x:c>
       <x:c r="D63" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E63" s="7" t="str">
-        <x:v>435 Crown St</x:v>
+        <x:v>Shop SP01, Westfield Tea Tree Plaza, 976 North East Road</x:v>
       </x:c>
       <x:c r="F63" s="7" t="str">
-        <x:v>Surry Hills</x:v>
+        <x:v>Modbury</x:v>
       </x:c>
       <x:c r="G63" s="7" t="n">
-        <x:v>2010</x:v>
+        <x:v>5092</x:v>
       </x:c>
       <x:c r="H63" s="7" t="str">
-        <x:v>02 9319 7525</x:v>
+        <x:v>08 8464 0712</x:v>
       </x:c>
       <x:c r="I63" s="7" t="str">
-        <x:v>surryhills@yochi.com.au</x:v>
+        <x:v>teatree@yochi.com</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="7" t="str">
-        <x:v>Yo-Chi Tea Tree Plaza</x:v>
+        <x:v>Yo-Chi The Esplanade Surfers Paradise</x:v>
       </x:c>
       <x:c r="B64" s="7" t="str">
-        <x:v>SA</x:v>
+        <x:v>QLD</x:v>
       </x:c>
       <x:c r="C64" s="7" t="str">
-        <x:v>2024-09-07</x:v>
+        <x:v>2024-05-10</x:v>
       </x:c>
       <x:c r="D64" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E64" s="7" t="str">
-        <x:v>Shop SP01, Westfield Tea Tree Plaza, 976 North East Road</x:v>
+        <x:v>Shop T1.05A,  Soul Board Walk,  4 Esplanade</x:v>
       </x:c>
       <x:c r="F64" s="7" t="str">
-        <x:v>Modbury</x:v>
+        <x:v>Surfers Paradise</x:v>
       </x:c>
       <x:c r="G64" s="7" t="n">
-        <x:v>5092</x:v>
+        <x:v>4217</x:v>
       </x:c>
       <x:c r="H64" s="7" t="str">
-        <x:v>08 8464 0712</x:v>
+        <x:v>07 5655 0199</x:v>
       </x:c>
       <x:c r="I64" s="7" t="str">
-        <x:v>teatree@yochi.com</x:v>
+        <x:v>soulboardwalk@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="7" t="str">
-        <x:v>Yo-Chi The Esplanade Surfers Paradise</x:v>
+        <x:v>Yo-Chi Top Ryde</x:v>
       </x:c>
       <x:c r="B65" s="7" t="str">
-        <x:v>QLD</x:v>
+        <x:v>NSW</x:v>
       </x:c>
       <x:c r="C65" s="7" t="str">
-        <x:v>2024-05-10</x:v>
+        <x:v>2025-06-05</x:v>
       </x:c>
       <x:c r="D65" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E65" s="7" t="str">
-        <x:v>Shop T1.05A,  Soul Board Walk,  4 Esplanade</x:v>
+        <x:v>Shop R3004, Corner Devlin Street and Blaxland Road</x:v>
       </x:c>
       <x:c r="F65" s="7" t="str">
-        <x:v>Surfers Paradise</x:v>
+        <x:v>Ryde</x:v>
       </x:c>
       <x:c r="G65" s="7" t="n">
-        <x:v>4217</x:v>
+        <x:v>2112</x:v>
       </x:c>
       <x:c r="H65" s="7" t="str">
-        <x:v>07 5655 0199</x:v>
+        <x:v>02 9955 4825</x:v>
       </x:c>
       <x:c r="I65" s="7" t="str">
-        <x:v>soulboardwalk@yochi.com.au</x:v>
+        <x:v>topryde@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="7" t="str">
-        <x:v>Yo-Chi Top Ryde</x:v>
+        <x:v>Yo-Chi Vic Park</x:v>
       </x:c>
       <x:c r="B66" s="7" t="str">
-        <x:v>NSW</x:v>
+        <x:v>WA</x:v>
       </x:c>
       <x:c r="C66" s="7" t="str">
-        <x:v>2025-06-05</x:v>
+        <x:v>2022-12-06</x:v>
       </x:c>
       <x:c r="D66" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E66" s="7" t="str">
-        <x:v>Shop R3004, Corner Devlin Street and Blaxland Road</x:v>
+        <x:v>Shop1/896 Albany Hwy</x:v>
       </x:c>
       <x:c r="F66" s="7" t="str">
-        <x:v>Ryde</x:v>
+        <x:v>Victoria Park</x:v>
       </x:c>
       <x:c r="G66" s="7" t="n">
-        <x:v>2112</x:v>
+        <x:v>6100</x:v>
       </x:c>
       <x:c r="H66" s="7" t="str">
-        <x:v>02 9955 4825</x:v>
+        <x:v>08 6363 5510</x:v>
       </x:c>
       <x:c r="I66" s="7" t="str">
-        <x:v>topryde@yochi.com.au</x:v>
+        <x:v>victoriapark@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="7" t="str">
-        <x:v>Yo-Chi Vic Park</x:v>
+        <x:v>Yo-Chi West End</x:v>
       </x:c>
       <x:c r="B67" s="7" t="str">
-        <x:v>WA</x:v>
+        <x:v>QLD</x:v>
       </x:c>
       <x:c r="C67" s="7" t="str">
-        <x:v>2022-12-06</x:v>
+        <x:v>2025-05-12</x:v>
       </x:c>
       <x:c r="D67" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E67" s="7" t="str">
-        <x:v>Shop1/896 Albany Hwy</x:v>
+        <x:v>TG1B 115 Boundary St</x:v>
       </x:c>
       <x:c r="F67" s="7" t="str">
-        <x:v>Victoria Park</x:v>
+        <x:v>West End</x:v>
       </x:c>
       <x:c r="G67" s="7" t="n">
-        <x:v>6100</x:v>
+        <x:v>4101</x:v>
       </x:c>
       <x:c r="H67" s="7" t="str">
-        <x:v>08 6363 5510</x:v>
+        <x:v>07 3333 1796</x:v>
       </x:c>
       <x:c r="I67" s="7" t="str">
-        <x:v>victoriapark@yochi.com.au</x:v>
+        <x:v>westend@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="7" t="str">
-        <x:v>Yo-Chi West End</x:v>
+        <x:v>Yo-Chi Whitford City</x:v>
       </x:c>
       <x:c r="B68" s="7" t="str">
-        <x:v>QLD</x:v>
+        <x:v>WA</x:v>
       </x:c>
       <x:c r="C68" s="7" t="str">
-        <x:v>2025-05-12</x:v>
+        <x:v>2024-12-15</x:v>
       </x:c>
       <x:c r="D68" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E68" s="7" t="str">
-        <x:v>TG1B 115 Boundary St</x:v>
+        <x:v>Shop 321 Corner of Marmion &amp; Whitford Aves</x:v>
       </x:c>
       <x:c r="F68" s="7" t="str">
-        <x:v>West End</x:v>
+        <x:v>Hillarys</x:v>
       </x:c>
       <x:c r="G68" s="7" t="n">
-        <x:v>4101</x:v>
+        <x:v>6025</x:v>
       </x:c>
       <x:c r="H68" s="7" t="str">
-        <x:v>07 3333 1796</x:v>
+        <x:v>08 6363 5266</x:v>
       </x:c>
       <x:c r="I68" s="7" t="str">
-        <x:v>westend@yochi.com.au</x:v>
+        <x:v>whitfordcity@yochi.com.au</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="7" t="str">
-        <x:v>Yo-Chi Whitford City</x:v>
+        <x:v>Yo-Chi Windsor</x:v>
       </x:c>
       <x:c r="B69" s="7" t="str">
-        <x:v>WA</x:v>
+        <x:v>VIC</x:v>
       </x:c>
       <x:c r="C69" s="7" t="str">
-        <x:v>2024-12-15</x:v>
+        <x:v>2022-08-14</x:v>
       </x:c>
       <x:c r="D69" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E69" s="7" t="str">
-        <x:v>Shop 321 Corner of Marmion &amp; Whitford Aves</x:v>
+        <x:v>127 Chapel St</x:v>
       </x:c>
       <x:c r="F69" s="7" t="str">
-        <x:v>Hillarys</x:v>
+        <x:v>Windsor</x:v>
       </x:c>
       <x:c r="G69" s="7" t="n">
-        <x:v>6025</x:v>
+        <x:v>3181</x:v>
       </x:c>
       <x:c r="H69" s="7" t="str">
-        <x:v>08 6363 5266</x:v>
+        <x:v>03 8644 1312</x:v>
       </x:c>
       <x:c r="I69" s="7" t="str">
-        <x:v>whitfordcity@yochi.com.au</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70">
-      <x:c r="A70" s="7" t="str">
-        <x:v>Yo-Chi Windsor</x:v>
-      </x:c>
-      <x:c r="B70" s="7" t="str">
-        <x:v>VIC</x:v>
-      </x:c>
-      <x:c r="C70" s="7" t="str">
-        <x:v>2022-08-14</x:v>
-      </x:c>
-      <x:c r="D70" s="7" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="E70" s="7" t="str">
-        <x:v>127 Chapel St</x:v>
-      </x:c>
-      <x:c r="F70" s="7" t="str">
-        <x:v>Windsor</x:v>
-      </x:c>
-      <x:c r="G70" s="7" t="n">
-        <x:v>3181</x:v>
-      </x:c>
-      <x:c r="H70" s="7" t="str">
-        <x:v>03 8644 1312</x:v>
-      </x:c>
-      <x:c r="I70" s="7" t="str">
         <x:v>windsor@yochi.com.au</x:v>
       </x:c>
     </x:row>
@@ -3115,7 +3096,7 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="7" t="str">
-        <x:v>Yo-Chi Charlestown</x:v>
+        <x:v>Yo-Chi Chatswood</x:v>
       </x:c>
       <x:c r="B15" s="7" t="n">
         <x:v>0.4</x:v>
@@ -3174,7 +3155,7 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="7" t="str">
-        <x:v>Yo-Chi Chatswood</x:v>
+        <x:v>Yo-Chi Chevron Surfers Paradise</x:v>
       </x:c>
       <x:c r="B16" s="7" t="n">
         <x:v>0.4</x:v>
@@ -3233,7 +3214,7 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="7" t="str">
-        <x:v>Yo-Chi Chevron Surfers Paradise</x:v>
+        <x:v>Yo-Chi Chippendale</x:v>
       </x:c>
       <x:c r="B17" s="7" t="n">
         <x:v>0.4</x:v>
@@ -3292,7 +3273,7 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="7" t="str">
-        <x:v>Yo-Chi Chippendale</x:v>
+        <x:v>Yo-Chi Circular Quay</x:v>
       </x:c>
       <x:c r="B18" s="7" t="n">
         <x:v>0.4</x:v>
@@ -3351,7 +3332,7 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="7" t="str">
-        <x:v>Yo-Chi Circular Quay</x:v>
+        <x:v>Yo-Chi Claremont</x:v>
       </x:c>
       <x:c r="B19" s="7" t="n">
         <x:v>0.4</x:v>
@@ -3410,7 +3391,7 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="7" t="str">
-        <x:v>Yo-Chi Claremont</x:v>
+        <x:v>Yo-Chi Cockburn Central</x:v>
       </x:c>
       <x:c r="B20" s="7" t="n">
         <x:v>0.4</x:v>
@@ -3469,7 +3450,7 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="7" t="str">
-        <x:v>Yo-Chi Cockburn Central</x:v>
+        <x:v>Yo-Chi Coogee</x:v>
       </x:c>
       <x:c r="B21" s="7" t="n">
         <x:v>0.4</x:v>
@@ -3528,7 +3509,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="7" t="str">
-        <x:v>Yo-Chi Coogee</x:v>
+        <x:v>Yo-Chi Cronulla</x:v>
       </x:c>
       <x:c r="B22" s="7" t="n">
         <x:v>0.4</x:v>
@@ -3587,7 +3568,7 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="7" t="str">
-        <x:v>Yo-Chi Cronulla</x:v>
+        <x:v>Yo-Chi Currambine</x:v>
       </x:c>
       <x:c r="B23" s="7" t="n">
         <x:v>0.4</x:v>
@@ -3646,7 +3627,7 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="7" t="str">
-        <x:v>Yo-Chi Currambine</x:v>
+        <x:v>Yo-Chi Double Bay</x:v>
       </x:c>
       <x:c r="B24" s="7" t="n">
         <x:v>0.4</x:v>
@@ -3705,7 +3686,7 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="7" t="str">
-        <x:v>Yo-Chi Double Bay</x:v>
+        <x:v>Yo-Chi Eastland</x:v>
       </x:c>
       <x:c r="B25" s="7" t="n">
         <x:v>0.4</x:v>
@@ -3764,7 +3745,7 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="7" t="str">
-        <x:v>Yo-Chi Eastland</x:v>
+        <x:v>Yo-Chi Forrest Chase</x:v>
       </x:c>
       <x:c r="B26" s="7" t="n">
         <x:v>0.4</x:v>
@@ -3823,7 +3804,7 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="7" t="str">
-        <x:v>Yo-Chi Forrest Chase</x:v>
+        <x:v>Yo-Chi Fremantle</x:v>
       </x:c>
       <x:c r="B27" s="7" t="n">
         <x:v>0.4</x:v>
@@ -3882,7 +3863,7 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="7" t="str">
-        <x:v>Yo-Chi Fremantle</x:v>
+        <x:v>Yo-Chi Gasworks</x:v>
       </x:c>
       <x:c r="B28" s="7" t="n">
         <x:v>0.4</x:v>
@@ -3941,7 +3922,7 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="7" t="str">
-        <x:v>Yo-Chi Gasworks</x:v>
+        <x:v>Yo-Chi George St</x:v>
       </x:c>
       <x:c r="B29" s="7" t="n">
         <x:v>0.4</x:v>
@@ -4000,7 +3981,7 @@
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="7" t="str">
-        <x:v>Yo-Chi George St</x:v>
+        <x:v>Yo-Chi Glenelg</x:v>
       </x:c>
       <x:c r="B30" s="7" t="n">
         <x:v>0.4</x:v>
@@ -4059,7 +4040,7 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="7" t="str">
-        <x:v>Yo-Chi Glenelg</x:v>
+        <x:v>Yo-Chi Gouger St</x:v>
       </x:c>
       <x:c r="B31" s="7" t="n">
         <x:v>0.4</x:v>
@@ -4118,7 +4099,7 @@
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="7" t="str">
-        <x:v>Yo-Chi Gouger St</x:v>
+        <x:v>Yo-Chi Harbour Town</x:v>
       </x:c>
       <x:c r="B32" s="7" t="n">
         <x:v>0.4</x:v>
@@ -4177,7 +4158,7 @@
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="7" t="str">
-        <x:v>Yo-Chi Harbour Town</x:v>
+        <x:v>Yo-Chi Hawthorn</x:v>
       </x:c>
       <x:c r="B33" s="7" t="n">
         <x:v>0.4</x:v>
@@ -4236,7 +4217,7 @@
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="7" t="str">
-        <x:v>Yo-Chi Hawthorn</x:v>
+        <x:v>Yo-Chi Henley Beach</x:v>
       </x:c>
       <x:c r="B34" s="7" t="n">
         <x:v>0.4</x:v>
@@ -4295,7 +4276,7 @@
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="7" t="str">
-        <x:v>Yo-Chi Henley Beach</x:v>
+        <x:v>Yo-Chi Highgate</x:v>
       </x:c>
       <x:c r="B35" s="7" t="n">
         <x:v>0.4</x:v>
@@ -4354,7 +4335,7 @@
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="7" t="str">
-        <x:v>Yo-Chi Highgate</x:v>
+        <x:v>Yo-Chi Highpoint</x:v>
       </x:c>
       <x:c r="B36" s="7" t="n">
         <x:v>0.4</x:v>
@@ -4413,7 +4394,7 @@
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="7" t="str">
-        <x:v>Yo-Chi Highpoint</x:v>
+        <x:v>Yo-Chi Indooroopilly</x:v>
       </x:c>
       <x:c r="B37" s="7" t="n">
         <x:v>0.4</x:v>
@@ -4472,7 +4453,7 @@
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="7" t="str">
-        <x:v>Yo-Chi Indooroopilly</x:v>
+        <x:v>Yo-Chi Karrinyup</x:v>
       </x:c>
       <x:c r="B38" s="7" t="n">
         <x:v>0.4</x:v>
@@ -4531,7 +4512,7 @@
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="7" t="str">
-        <x:v>Yo-Chi Karrinyup</x:v>
+        <x:v>Yo-Chi Kawana Waters</x:v>
       </x:c>
       <x:c r="B39" s="7" t="n">
         <x:v>0.4</x:v>
@@ -4590,7 +4571,7 @@
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="7" t="str">
-        <x:v>Yo-Chi Kawana Waters</x:v>
+        <x:v>Yo-Chi Lane Cove</x:v>
       </x:c>
       <x:c r="B40" s="7" t="n">
         <x:v>0.4</x:v>
@@ -4649,7 +4630,7 @@
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="7" t="str">
-        <x:v>Yo-Chi Lane Cove</x:v>
+        <x:v>Yo-Chi Leederville</x:v>
       </x:c>
       <x:c r="B41" s="7" t="n">
         <x:v>0.4</x:v>
@@ -4708,7 +4689,7 @@
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="7" t="str">
-        <x:v>Yo-Chi Leederville</x:v>
+        <x:v>Yo-Chi Macquarie</x:v>
       </x:c>
       <x:c r="B42" s="7" t="n">
         <x:v>0.4</x:v>
@@ -4767,7 +4748,7 @@
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="7" t="str">
-        <x:v>Yo-Chi Macquarie</x:v>
+        <x:v>Yo-Chi Malvern</x:v>
       </x:c>
       <x:c r="B43" s="7" t="n">
         <x:v>0.4</x:v>
@@ -4826,7 +4807,7 @@
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="7" t="str">
-        <x:v>Yo-Chi Malvern</x:v>
+        <x:v>Yo-Chi Mandurah</x:v>
       </x:c>
       <x:c r="B44" s="7" t="n">
         <x:v>0.4</x:v>
@@ -4885,7 +4866,7 @@
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="7" t="str">
-        <x:v>Yo-Chi Mandurah</x:v>
+        <x:v>Yo-Chi Manly</x:v>
       </x:c>
       <x:c r="B45" s="7" t="n">
         <x:v>0.4</x:v>
@@ -4944,7 +4925,7 @@
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="7" t="str">
-        <x:v>Yo-Chi Manly</x:v>
+        <x:v>Yo-Chi Mt Gravatt</x:v>
       </x:c>
       <x:c r="B46" s="7" t="n">
         <x:v>0.4</x:v>
@@ -5003,7 +4984,7 @@
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="7" t="str">
-        <x:v>Yo-Chi Mt Gravatt</x:v>
+        <x:v>Yo-Chi Newtown</x:v>
       </x:c>
       <x:c r="B47" s="7" t="n">
         <x:v>0.4</x:v>
@@ -5062,7 +5043,7 @@
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="7" t="str">
-        <x:v>Yo-Chi Newtown</x:v>
+        <x:v>Yo-Chi Noosa</x:v>
       </x:c>
       <x:c r="B48" s="7" t="n">
         <x:v>0.4</x:v>
@@ -5121,7 +5102,7 @@
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="7" t="str">
-        <x:v>Yo-Chi Noosa</x:v>
+        <x:v>Yo-Chi Norwood</x:v>
       </x:c>
       <x:c r="B49" s="7" t="n">
         <x:v>0.4</x:v>
@@ -5180,7 +5161,7 @@
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="7" t="str">
-        <x:v>Yo-Chi Norwood</x:v>
+        <x:v>Yo-Chi Paddington</x:v>
       </x:c>
       <x:c r="B50" s="7" t="n">
         <x:v>0.4</x:v>
@@ -5239,7 +5220,7 @@
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="7" t="str">
-        <x:v>Yo-Chi Paddington</x:v>
+        <x:v>Yo-Chi Penrith</x:v>
       </x:c>
       <x:c r="B51" s="7" t="n">
         <x:v>0.4</x:v>
@@ -5298,7 +5279,7 @@
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="7" t="str">
-        <x:v>Yo-Chi Penrith</x:v>
+        <x:v>Yo-Chi Prospect</x:v>
       </x:c>
       <x:c r="B52" s="7" t="n">
         <x:v>0.4</x:v>
@@ -5357,7 +5338,7 @@
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="7" t="str">
-        <x:v>Yo-Chi Prospect</x:v>
+        <x:v>Yo-Chi QV</x:v>
       </x:c>
       <x:c r="B53" s="7" t="n">
         <x:v>0.4</x:v>
@@ -5416,7 +5397,7 @@
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="7" t="str">
-        <x:v>Yo-Chi QV</x:v>
+        <x:v>Yo-Chi Randwick</x:v>
       </x:c>
       <x:c r="B54" s="7" t="n">
         <x:v>0.4</x:v>
@@ -5475,7 +5456,7 @@
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="7" t="str">
-        <x:v>Yo-Chi Randwick</x:v>
+        <x:v>Yo-Chi Robina</x:v>
       </x:c>
       <x:c r="B55" s="7" t="n">
         <x:v>0.4</x:v>
@@ -5534,7 +5515,7 @@
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="7" t="str">
-        <x:v>Yo-Chi Robina</x:v>
+        <x:v>Yo-Chi Rouse Hill</x:v>
       </x:c>
       <x:c r="B56" s="7" t="n">
         <x:v>0.4</x:v>
@@ -5593,7 +5574,7 @@
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="7" t="str">
-        <x:v>Yo-Chi Rouse Hill</x:v>
+        <x:v>Yo-Chi Semaphore</x:v>
       </x:c>
       <x:c r="B57" s="7" t="n">
         <x:v>0.4</x:v>
@@ -5652,7 +5633,7 @@
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="7" t="str">
-        <x:v>Yo-Chi Semaphore</x:v>
+        <x:v>Yo-Chi South Perth</x:v>
       </x:c>
       <x:c r="B58" s="7" t="n">
         <x:v>0.4</x:v>
@@ -5711,7 +5692,7 @@
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="7" t="str">
-        <x:v>Yo-Chi South Perth</x:v>
+        <x:v>Yo-Chi Southbank</x:v>
       </x:c>
       <x:c r="B59" s="7" t="n">
         <x:v>0.4</x:v>
@@ -5770,7 +5751,7 @@
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="7" t="str">
-        <x:v>Yo-Chi Southbank</x:v>
+        <x:v>Yo-Chi Southland</x:v>
       </x:c>
       <x:c r="B60" s="7" t="n">
         <x:v>0.4</x:v>
@@ -5829,7 +5810,7 @@
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="7" t="str">
-        <x:v>Yo-Chi Southland</x:v>
+        <x:v>Yo-Chi Sunshine Plaza</x:v>
       </x:c>
       <x:c r="B61" s="7" t="n">
         <x:v>0.4</x:v>
@@ -5888,7 +5869,7 @@
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="7" t="str">
-        <x:v>Yo-Chi Sunshine Plaza</x:v>
+        <x:v>Yo-Chi Surry Hills</x:v>
       </x:c>
       <x:c r="B62" s="7" t="n">
         <x:v>0.4</x:v>
@@ -5947,7 +5928,7 @@
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="7" t="str">
-        <x:v>Yo-Chi Surry Hills</x:v>
+        <x:v>Yo-Chi Tea Tree Plaza</x:v>
       </x:c>
       <x:c r="B63" s="7" t="n">
         <x:v>0.4</x:v>
@@ -6006,7 +5987,7 @@
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="7" t="str">
-        <x:v>Yo-Chi Tea Tree Plaza</x:v>
+        <x:v>Yo-Chi The Esplanade Surfers Paradise</x:v>
       </x:c>
       <x:c r="B64" s="7" t="n">
         <x:v>0.4</x:v>
@@ -6065,7 +6046,7 @@
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="7" t="str">
-        <x:v>Yo-Chi The Esplanade Surfers Paradise</x:v>
+        <x:v>Yo-Chi Top Ryde</x:v>
       </x:c>
       <x:c r="B65" s="7" t="n">
         <x:v>0.4</x:v>
@@ -6124,7 +6105,7 @@
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="7" t="str">
-        <x:v>Yo-Chi Top Ryde</x:v>
+        <x:v>Yo-Chi Vic Park</x:v>
       </x:c>
       <x:c r="B66" s="7" t="n">
         <x:v>0.4</x:v>
@@ -6183,7 +6164,7 @@
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="7" t="str">
-        <x:v>Yo-Chi Vic Park</x:v>
+        <x:v>Yo-Chi West End</x:v>
       </x:c>
       <x:c r="B67" s="7" t="n">
         <x:v>0.4</x:v>
@@ -6242,7 +6223,7 @@
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="7" t="str">
-        <x:v>Yo-Chi West End</x:v>
+        <x:v>Yo-Chi Whitford City</x:v>
       </x:c>
       <x:c r="B68" s="7" t="n">
         <x:v>0.4</x:v>
@@ -6301,7 +6282,7 @@
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="7" t="str">
-        <x:v>Yo-Chi Whitford City</x:v>
+        <x:v>Yo-Chi Windsor</x:v>
       </x:c>
       <x:c r="B69" s="7" t="n">
         <x:v>0.4</x:v>
@@ -6360,61 +6341,6413 @@
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="7" t="str">
-        <x:v>Yo-Chi Windsor</x:v>
+        <x:v>Yo-Chi New Venue 01</x:v>
       </x:c>
       <x:c r="B70" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C70" s="7" t="n">
         <x:v>0.4</x:v>
       </x:c>
-      <x:c r="C70" s="7" t="n">
-        <x:v>0.4353</x:v>
-      </x:c>
       <x:c r="D70" s="7" t="n">
-        <x:v>0.4706</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="E70" s="7" t="n">
-        <x:v>0.5059</x:v>
+        <x:v>0.55</x:v>
       </x:c>
       <x:c r="F70" s="7" t="n">
-        <x:v>0.5412</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="G70" s="7" t="n">
-        <x:v>0.5765</x:v>
+        <x:v>0.65</x:v>
       </x:c>
       <x:c r="H70" s="7" t="n">
-        <x:v>0.6118</x:v>
+        <x:v>0.7</x:v>
       </x:c>
       <x:c r="I70" s="7" t="n">
-        <x:v>0.6471</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="J70" s="7" t="n">
-        <x:v>0.6824</x:v>
+        <x:v>0.78</x:v>
       </x:c>
       <x:c r="K70" s="7" t="n">
-        <x:v>0.7176</x:v>
+        <x:v>0.82</x:v>
       </x:c>
       <x:c r="L70" s="7" t="n">
-        <x:v>0.7529</x:v>
+        <x:v>0.85</x:v>
       </x:c>
       <x:c r="M70" s="7" t="n">
-        <x:v>0.7882</x:v>
+        <x:v>0.88</x:v>
       </x:c>
       <x:c r="N70" s="7" t="n">
-        <x:v>0.8235</x:v>
+        <x:v>0.9</x:v>
       </x:c>
       <x:c r="O70" s="7" t="n">
-        <x:v>0.8588</x:v>
+        <x:v>0.92</x:v>
       </x:c>
       <x:c r="P70" s="7" t="n">
-        <x:v>0.8941</x:v>
+        <x:v>0.94</x:v>
       </x:c>
       <x:c r="Q70" s="7" t="n">
-        <x:v>0.9294</x:v>
+        <x:v>0.96</x:v>
       </x:c>
       <x:c r="R70" s="7" t="n">
-        <x:v>0.9647</x:v>
+        <x:v>0.98</x:v>
       </x:c>
       <x:c r="S70" s="7" t="n">
         <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="7" t="str">
+        <x:v>Yo-Chi New Venue 02</x:v>
+      </x:c>
+      <x:c r="B71" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C71" s="7" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="D71" s="7" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="E71" s="7" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="F71" s="7" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="G71" s="7" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="H71" s="7" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="I71" s="7" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="J71" s="7" t="n">
+        <x:v>0.78</x:v>
+      </x:c>
+      <x:c r="K71" s="7" t="n">
+        <x:v>0.82</x:v>
+      </x:c>
+      <x:c r="L71" s="7" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="M71" s="7" t="n">
+        <x:v>0.88</x:v>
+      </x:c>
+      <x:c r="N71" s="7" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="O71" s="7" t="n">
+        <x:v>0.92</x:v>
+      </x:c>
+      <x:c r="P71" s="7" t="n">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="Q71" s="7" t="n">
+        <x:v>0.96</x:v>
+      </x:c>
+      <x:c r="R71" s="7" t="n">
+        <x:v>0.98</x:v>
+      </x:c>
+      <x:c r="S71" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="7" t="str">
+        <x:v>Yo-Chi New Venue 03</x:v>
+      </x:c>
+      <x:c r="B72" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C72" s="7" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="D72" s="7" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="E72" s="7" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="F72" s="7" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="G72" s="7" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="H72" s="7" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="I72" s="7" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="J72" s="7" t="n">
+        <x:v>0.78</x:v>
+      </x:c>
+      <x:c r="K72" s="7" t="n">
+        <x:v>0.82</x:v>
+      </x:c>
+      <x:c r="L72" s="7" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="M72" s="7" t="n">
+        <x:v>0.88</x:v>
+      </x:c>
+      <x:c r="N72" s="7" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="O72" s="7" t="n">
+        <x:v>0.92</x:v>
+      </x:c>
+      <x:c r="P72" s="7" t="n">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="Q72" s="7" t="n">
+        <x:v>0.96</x:v>
+      </x:c>
+      <x:c r="R72" s="7" t="n">
+        <x:v>0.98</x:v>
+      </x:c>
+      <x:c r="S72" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="7" t="str">
+        <x:v>Yo-Chi New Venue 04</x:v>
+      </x:c>
+      <x:c r="B73" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C73" s="7" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="D73" s="7" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="E73" s="7" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="F73" s="7" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="G73" s="7" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="H73" s="7" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="I73" s="7" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="J73" s="7" t="n">
+        <x:v>0.78</x:v>
+      </x:c>
+      <x:c r="K73" s="7" t="n">
+        <x:v>0.82</x:v>
+      </x:c>
+      <x:c r="L73" s="7" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="M73" s="7" t="n">
+        <x:v>0.88</x:v>
+      </x:c>
+      <x:c r="N73" s="7" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="O73" s="7" t="n">
+        <x:v>0.92</x:v>
+      </x:c>
+      <x:c r="P73" s="7" t="n">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="Q73" s="7" t="n">
+        <x:v>0.96</x:v>
+      </x:c>
+      <x:c r="R73" s="7" t="n">
+        <x:v>0.98</x:v>
+      </x:c>
+      <x:c r="S73" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="7" t="str">
+        <x:v>Yo-Chi New Venue 05</x:v>
+      </x:c>
+      <x:c r="B74" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C74" s="7" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="D74" s="7" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="E74" s="7" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="F74" s="7" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="G74" s="7" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="H74" s="7" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="I74" s="7" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="J74" s="7" t="n">
+        <x:v>0.78</x:v>
+      </x:c>
+      <x:c r="K74" s="7" t="n">
+        <x:v>0.82</x:v>
+      </x:c>
+      <x:c r="L74" s="7" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="M74" s="7" t="n">
+        <x:v>0.88</x:v>
+      </x:c>
+      <x:c r="N74" s="7" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="O74" s="7" t="n">
+        <x:v>0.92</x:v>
+      </x:c>
+      <x:c r="P74" s="7" t="n">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="Q74" s="7" t="n">
+        <x:v>0.96</x:v>
+      </x:c>
+      <x:c r="R74" s="7" t="n">
+        <x:v>0.98</x:v>
+      </x:c>
+      <x:c r="S74" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="7" t="str">
+        <x:v>Yo-Chi New Venue 06</x:v>
+      </x:c>
+      <x:c r="B75" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C75" s="7" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="D75" s="7" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="E75" s="7" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="F75" s="7" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="G75" s="7" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="H75" s="7" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="I75" s="7" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="J75" s="7" t="n">
+        <x:v>0.78</x:v>
+      </x:c>
+      <x:c r="K75" s="7" t="n">
+        <x:v>0.82</x:v>
+      </x:c>
+      <x:c r="L75" s="7" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="M75" s="7" t="n">
+        <x:v>0.88</x:v>
+      </x:c>
+      <x:c r="N75" s="7" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="O75" s="7" t="n">
+        <x:v>0.92</x:v>
+      </x:c>
+      <x:c r="P75" s="7" t="n">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="Q75" s="7" t="n">
+        <x:v>0.96</x:v>
+      </x:c>
+      <x:c r="R75" s="7" t="n">
+        <x:v>0.98</x:v>
+      </x:c>
+      <x:c r="S75" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="7" t="str">
+        <x:v>Yo-Chi New Venue 07</x:v>
+      </x:c>
+      <x:c r="B76" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C76" s="7" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="D76" s="7" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="E76" s="7" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="F76" s="7" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="G76" s="7" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="H76" s="7" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="I76" s="7" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="J76" s="7" t="n">
+        <x:v>0.78</x:v>
+      </x:c>
+      <x:c r="K76" s="7" t="n">
+        <x:v>0.82</x:v>
+      </x:c>
+      <x:c r="L76" s="7" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="M76" s="7" t="n">
+        <x:v>0.88</x:v>
+      </x:c>
+      <x:c r="N76" s="7" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="O76" s="7" t="n">
+        <x:v>0.92</x:v>
+      </x:c>
+      <x:c r="P76" s="7" t="n">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="Q76" s="7" t="n">
+        <x:v>0.96</x:v>
+      </x:c>
+      <x:c r="R76" s="7" t="n">
+        <x:v>0.98</x:v>
+      </x:c>
+      <x:c r="S76" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="7" t="str">
+        <x:v>Yo-Chi New Venue 08</x:v>
+      </x:c>
+      <x:c r="B77" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C77" s="7" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="D77" s="7" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="E77" s="7" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="F77" s="7" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="G77" s="7" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="H77" s="7" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="I77" s="7" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="J77" s="7" t="n">
+        <x:v>0.78</x:v>
+      </x:c>
+      <x:c r="K77" s="7" t="n">
+        <x:v>0.82</x:v>
+      </x:c>
+      <x:c r="L77" s="7" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="M77" s="7" t="n">
+        <x:v>0.88</x:v>
+      </x:c>
+      <x:c r="N77" s="7" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="O77" s="7" t="n">
+        <x:v>0.92</x:v>
+      </x:c>
+      <x:c r="P77" s="7" t="n">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="Q77" s="7" t="n">
+        <x:v>0.96</x:v>
+      </x:c>
+      <x:c r="R77" s="7" t="n">
+        <x:v>0.98</x:v>
+      </x:c>
+      <x:c r="S77" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="7" t="str">
+        <x:v>Yo-Chi New Venue 09</x:v>
+      </x:c>
+      <x:c r="B78" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C78" s="7" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="D78" s="7" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="E78" s="7" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="F78" s="7" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="G78" s="7" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="H78" s="7" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="I78" s="7" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="J78" s="7" t="n">
+        <x:v>0.78</x:v>
+      </x:c>
+      <x:c r="K78" s="7" t="n">
+        <x:v>0.82</x:v>
+      </x:c>
+      <x:c r="L78" s="7" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="M78" s="7" t="n">
+        <x:v>0.88</x:v>
+      </x:c>
+      <x:c r="N78" s="7" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="O78" s="7" t="n">
+        <x:v>0.92</x:v>
+      </x:c>
+      <x:c r="P78" s="7" t="n">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="Q78" s="7" t="n">
+        <x:v>0.96</x:v>
+      </x:c>
+      <x:c r="R78" s="7" t="n">
+        <x:v>0.98</x:v>
+      </x:c>
+      <x:c r="S78" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="7" t="str">
+        <x:v>Yo-Chi New Venue 10</x:v>
+      </x:c>
+      <x:c r="B79" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C79" s="7" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="D79" s="7" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="E79" s="7" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="F79" s="7" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="G79" s="7" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="H79" s="7" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="I79" s="7" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="J79" s="7" t="n">
+        <x:v>0.78</x:v>
+      </x:c>
+      <x:c r="K79" s="7" t="n">
+        <x:v>0.82</x:v>
+      </x:c>
+      <x:c r="L79" s="7" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="M79" s="7" t="n">
+        <x:v>0.88</x:v>
+      </x:c>
+      <x:c r="N79" s="7" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="O79" s="7" t="n">
+        <x:v>0.92</x:v>
+      </x:c>
+      <x:c r="P79" s="7" t="n">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="Q79" s="7" t="n">
+        <x:v>0.96</x:v>
+      </x:c>
+      <x:c r="R79" s="7" t="n">
+        <x:v>0.98</x:v>
+      </x:c>
+      <x:c r="S79" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="7" t="str">
+        <x:v>Yo-Chi New Venue 11</x:v>
+      </x:c>
+      <x:c r="B80" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C80" s="7" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="D80" s="7" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="E80" s="7" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="F80" s="7" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="G80" s="7" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="H80" s="7" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="I80" s="7" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="J80" s="7" t="n">
+        <x:v>0.78</x:v>
+      </x:c>
+      <x:c r="K80" s="7" t="n">
+        <x:v>0.82</x:v>
+      </x:c>
+      <x:c r="L80" s="7" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="M80" s="7" t="n">
+        <x:v>0.88</x:v>
+      </x:c>
+      <x:c r="N80" s="7" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="O80" s="7" t="n">
+        <x:v>0.92</x:v>
+      </x:c>
+      <x:c r="P80" s="7" t="n">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="Q80" s="7" t="n">
+        <x:v>0.96</x:v>
+      </x:c>
+      <x:c r="R80" s="7" t="n">
+        <x:v>0.98</x:v>
+      </x:c>
+      <x:c r="S80" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="7" t="str">
+        <x:v>Yo-Chi New Venue 12</x:v>
+      </x:c>
+      <x:c r="B81" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C81" s="7" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="D81" s="7" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="E81" s="7" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="F81" s="7" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="G81" s="7" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="H81" s="7" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="I81" s="7" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="J81" s="7" t="n">
+        <x:v>0.78</x:v>
+      </x:c>
+      <x:c r="K81" s="7" t="n">
+        <x:v>0.82</x:v>
+      </x:c>
+      <x:c r="L81" s="7" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="M81" s="7" t="n">
+        <x:v>0.88</x:v>
+      </x:c>
+      <x:c r="N81" s="7" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="O81" s="7" t="n">
+        <x:v>0.92</x:v>
+      </x:c>
+      <x:c r="P81" s="7" t="n">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="Q81" s="7" t="n">
+        <x:v>0.96</x:v>
+      </x:c>
+      <x:c r="R81" s="7" t="n">
+        <x:v>0.98</x:v>
+      </x:c>
+      <x:c r="S81" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="7" t="str">
+        <x:v>Yo-Chi New Venue 13</x:v>
+      </x:c>
+      <x:c r="B82" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C82" s="7" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="D82" s="7" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="E82" s="7" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="F82" s="7" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="G82" s="7" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="H82" s="7" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="I82" s="7" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="J82" s="7" t="n">
+        <x:v>0.78</x:v>
+      </x:c>
+      <x:c r="K82" s="7" t="n">
+        <x:v>0.82</x:v>
+      </x:c>
+      <x:c r="L82" s="7" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="M82" s="7" t="n">
+        <x:v>0.88</x:v>
+      </x:c>
+      <x:c r="N82" s="7" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="O82" s="7" t="n">
+        <x:v>0.92</x:v>
+      </x:c>
+      <x:c r="P82" s="7" t="n">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="Q82" s="7" t="n">
+        <x:v>0.96</x:v>
+      </x:c>
+      <x:c r="R82" s="7" t="n">
+        <x:v>0.98</x:v>
+      </x:c>
+      <x:c r="S82" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="7" t="str">
+        <x:v>Yo-Chi New Venue 14</x:v>
+      </x:c>
+      <x:c r="B83" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C83" s="7" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="D83" s="7" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="E83" s="7" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="F83" s="7" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="G83" s="7" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="H83" s="7" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="I83" s="7" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="J83" s="7" t="n">
+        <x:v>0.78</x:v>
+      </x:c>
+      <x:c r="K83" s="7" t="n">
+        <x:v>0.82</x:v>
+      </x:c>
+      <x:c r="L83" s="7" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="M83" s="7" t="n">
+        <x:v>0.88</x:v>
+      </x:c>
+      <x:c r="N83" s="7" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="O83" s="7" t="n">
+        <x:v>0.92</x:v>
+      </x:c>
+      <x:c r="P83" s="7" t="n">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="Q83" s="7" t="n">
+        <x:v>0.96</x:v>
+      </x:c>
+      <x:c r="R83" s="7" t="n">
+        <x:v>0.98</x:v>
+      </x:c>
+      <x:c r="S83" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="7" t="str">
+        <x:v>Yo-Chi New Venue 15</x:v>
+      </x:c>
+      <x:c r="B84" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C84" s="7" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="D84" s="7" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="E84" s="7" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="F84" s="7" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="G84" s="7" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="H84" s="7" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="I84" s="7" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="J84" s="7" t="n">
+        <x:v>0.78</x:v>
+      </x:c>
+      <x:c r="K84" s="7" t="n">
+        <x:v>0.82</x:v>
+      </x:c>
+      <x:c r="L84" s="7" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="M84" s="7" t="n">
+        <x:v>0.88</x:v>
+      </x:c>
+      <x:c r="N84" s="7" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="O84" s="7" t="n">
+        <x:v>0.92</x:v>
+      </x:c>
+      <x:c r="P84" s="7" t="n">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="Q84" s="7" t="n">
+        <x:v>0.96</x:v>
+      </x:c>
+      <x:c r="R84" s="7" t="n">
+        <x:v>0.98</x:v>
+      </x:c>
+      <x:c r="S84" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="7" t="str">
+        <x:v>Yo-Chi New Venue 16</x:v>
+      </x:c>
+      <x:c r="B85" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C85" s="7" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="D85" s="7" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="E85" s="7" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="F85" s="7" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="G85" s="7" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="H85" s="7" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="I85" s="7" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="J85" s="7" t="n">
+        <x:v>0.78</x:v>
+      </x:c>
+      <x:c r="K85" s="7" t="n">
+        <x:v>0.82</x:v>
+      </x:c>
+      <x:c r="L85" s="7" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="M85" s="7" t="n">
+        <x:v>0.88</x:v>
+      </x:c>
+      <x:c r="N85" s="7" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="O85" s="7" t="n">
+        <x:v>0.92</x:v>
+      </x:c>
+      <x:c r="P85" s="7" t="n">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="Q85" s="7" t="n">
+        <x:v>0.96</x:v>
+      </x:c>
+      <x:c r="R85" s="7" t="n">
+        <x:v>0.98</x:v>
+      </x:c>
+      <x:c r="S85" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="7" t="str">
+        <x:v>Yo-Chi New Venue 17</x:v>
+      </x:c>
+      <x:c r="B86" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C86" s="7" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="D86" s="7" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="E86" s="7" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="F86" s="7" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="G86" s="7" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="H86" s="7" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="I86" s="7" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="J86" s="7" t="n">
+        <x:v>0.78</x:v>
+      </x:c>
+      <x:c r="K86" s="7" t="n">
+        <x:v>0.82</x:v>
+      </x:c>
+      <x:c r="L86" s="7" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="M86" s="7" t="n">
+        <x:v>0.88</x:v>
+      </x:c>
+      <x:c r="N86" s="7" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="O86" s="7" t="n">
+        <x:v>0.92</x:v>
+      </x:c>
+      <x:c r="P86" s="7" t="n">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="Q86" s="7" t="n">
+        <x:v>0.96</x:v>
+      </x:c>
+      <x:c r="R86" s="7" t="n">
+        <x:v>0.98</x:v>
+      </x:c>
+      <x:c r="S86" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="5" t="str">
+        <x:v>venue_name</x:v>
+      </x:c>
+      <x:c r="B1" s="9" t="str">
+        <x:v>Month 1</x:v>
+      </x:c>
+      <x:c r="C1" s="9" t="str">
+        <x:v>Month 2</x:v>
+      </x:c>
+      <x:c r="D1" s="9" t="str">
+        <x:v>Month 3</x:v>
+      </x:c>
+      <x:c r="E1" s="9" t="str">
+        <x:v>Month 4</x:v>
+      </x:c>
+      <x:c r="F1" s="9" t="str">
+        <x:v>Month 5</x:v>
+      </x:c>
+      <x:c r="G1" s="9" t="str">
+        <x:v>Month 6</x:v>
+      </x:c>
+      <x:c r="H1" s="9" t="str">
+        <x:v>Month 7</x:v>
+      </x:c>
+      <x:c r="I1" s="9" t="str">
+        <x:v>Month 8</x:v>
+      </x:c>
+      <x:c r="J1" s="9" t="str">
+        <x:v>Month 9</x:v>
+      </x:c>
+      <x:c r="K1" s="9" t="str">
+        <x:v>Month 10</x:v>
+      </x:c>
+      <x:c r="L1" s="9" t="str">
+        <x:v>Month 11</x:v>
+      </x:c>
+      <x:c r="M1" s="9" t="str">
+        <x:v>Month 12</x:v>
+      </x:c>
+      <x:c r="N1" s="9" t="str">
+        <x:v>Month 13</x:v>
+      </x:c>
+      <x:c r="O1" s="9" t="str">
+        <x:v>Month 14</x:v>
+      </x:c>
+      <x:c r="P1" s="9" t="str">
+        <x:v>Month 15</x:v>
+      </x:c>
+      <x:c r="Q1" s="9" t="str">
+        <x:v>Month 16</x:v>
+      </x:c>
+      <x:c r="R1" s="9" t="str">
+        <x:v>Month 17</x:v>
+      </x:c>
+      <x:c r="S1" s="9" t="str">
+        <x:v>Month 18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="7" t="str">
+        <x:v>Yo-Chi Albert St</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E2" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F2" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G2" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H2" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I2" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J2" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K2" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L2" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M2" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N2" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O2" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P2" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q2" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R2" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S2" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="7" t="str">
+        <x:v>Yo-Chi Balaclava</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F3" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G3" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I3" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J3" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K3" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L3" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M3" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N3" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O3" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P3" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q3" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R3" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S3" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="7" t="str">
+        <x:v>Yo-Chi Barangaroo</x:v>
+      </x:c>
+      <x:c r="B4" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C4" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D4" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E4" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F4" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G4" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H4" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I4" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J4" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K4" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L4" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M4" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N4" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O4" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P4" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q4" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R4" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S4" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="7" t="str">
+        <x:v>Yo-Chi Bondi</x:v>
+      </x:c>
+      <x:c r="B5" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C5" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D5" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E5" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F5" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G5" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H5" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I5" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J5" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K5" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L5" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M5" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N5" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O5" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P5" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q5" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R5" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S5" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="7" t="str">
+        <x:v>Yo-Chi Bondi Junction</x:v>
+      </x:c>
+      <x:c r="B6" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C6" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D6" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E6" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F6" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G6" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H6" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I6" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J6" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K6" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L6" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M6" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N6" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O6" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P6" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q6" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R6" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S6" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="7" t="str">
+        <x:v>Yo-Chi Brighton</x:v>
+      </x:c>
+      <x:c r="B7" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C7" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F7" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G7" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H7" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I7" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J7" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K7" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L7" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M7" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N7" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O7" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P7" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q7" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R7" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S7" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="7" t="str">
+        <x:v>Yo-Chi Broadbeach</x:v>
+      </x:c>
+      <x:c r="B8" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C8" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D8" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E8" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F8" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G8" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H8" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I8" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J8" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K8" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L8" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M8" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N8" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O8" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P8" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q8" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R8" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S8" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="7" t="str">
+        <x:v>Yo-Chi Bulimba</x:v>
+      </x:c>
+      <x:c r="B9" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C9" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D9" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E9" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F9" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G9" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H9" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I9" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J9" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K9" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L9" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M9" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N9" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O9" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P9" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q9" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R9" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S9" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="7" t="str">
+        <x:v>Yo-Chi Burleigh</x:v>
+      </x:c>
+      <x:c r="B10" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C10" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D10" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E10" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F10" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G10" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H10" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I10" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J10" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K10" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L10" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M10" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N10" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O10" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P10" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q10" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R10" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S10" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="7" t="str">
+        <x:v>Yo-Chi Burwood</x:v>
+      </x:c>
+      <x:c r="B11" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C11" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D11" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E11" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F11" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G11" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H11" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I11" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J11" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K11" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L11" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M11" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N11" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O11" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P11" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q11" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R11" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S11" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="7" t="str">
+        <x:v>Yo-Chi Carlton</x:v>
+      </x:c>
+      <x:c r="B12" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C12" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D12" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E12" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F12" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G12" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H12" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I12" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J12" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K12" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L12" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M12" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N12" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O12" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P12" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q12" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R12" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S12" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="7" t="str">
+        <x:v>Yo-Chi Castle Towers</x:v>
+      </x:c>
+      <x:c r="B13" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C13" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D13" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E13" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F13" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G13" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H13" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I13" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J13" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K13" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L13" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M13" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N13" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O13" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P13" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q13" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R13" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S13" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="7" t="str">
+        <x:v>Yo-Chi Chadstone</x:v>
+      </x:c>
+      <x:c r="B14" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C14" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D14" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E14" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F14" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G14" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H14" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I14" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J14" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K14" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L14" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M14" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N14" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O14" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P14" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q14" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R14" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S14" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="7" t="str">
+        <x:v>Yo-Chi Chatswood</x:v>
+      </x:c>
+      <x:c r="B15" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C15" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D15" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E15" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F15" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G15" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H15" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I15" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J15" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K15" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L15" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M15" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N15" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O15" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P15" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q15" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R15" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S15" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="7" t="str">
+        <x:v>Yo-Chi Chevron Surfers Paradise</x:v>
+      </x:c>
+      <x:c r="B16" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C16" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D16" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E16" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F16" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G16" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H16" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I16" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J16" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K16" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L16" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M16" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N16" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O16" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P16" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q16" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R16" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S16" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="7" t="str">
+        <x:v>Yo-Chi Chippendale</x:v>
+      </x:c>
+      <x:c r="B17" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C17" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D17" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E17" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F17" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G17" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H17" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I17" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J17" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K17" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L17" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M17" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N17" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O17" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P17" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q17" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R17" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S17" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="7" t="str">
+        <x:v>Yo-Chi Circular Quay</x:v>
+      </x:c>
+      <x:c r="B18" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C18" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D18" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E18" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F18" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G18" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H18" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I18" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J18" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K18" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L18" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M18" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N18" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O18" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P18" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q18" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R18" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S18" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="7" t="str">
+        <x:v>Yo-Chi Claremont</x:v>
+      </x:c>
+      <x:c r="B19" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C19" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D19" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E19" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F19" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G19" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H19" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I19" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J19" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K19" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L19" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M19" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N19" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O19" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P19" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q19" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R19" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S19" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="7" t="str">
+        <x:v>Yo-Chi Cockburn Central</x:v>
+      </x:c>
+      <x:c r="B20" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C20" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D20" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E20" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F20" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G20" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H20" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I20" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J20" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K20" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L20" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M20" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N20" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O20" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P20" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q20" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R20" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S20" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="7" t="str">
+        <x:v>Yo-Chi Coogee</x:v>
+      </x:c>
+      <x:c r="B21" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C21" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D21" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E21" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F21" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G21" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H21" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I21" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J21" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K21" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L21" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M21" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N21" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O21" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P21" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q21" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R21" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S21" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="7" t="str">
+        <x:v>Yo-Chi Cronulla</x:v>
+      </x:c>
+      <x:c r="B22" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C22" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D22" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E22" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F22" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G22" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H22" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I22" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J22" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K22" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L22" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M22" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N22" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O22" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P22" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q22" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R22" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S22" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="7" t="str">
+        <x:v>Yo-Chi Currambine</x:v>
+      </x:c>
+      <x:c r="B23" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C23" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D23" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E23" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F23" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G23" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H23" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I23" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J23" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K23" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L23" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M23" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N23" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O23" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P23" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q23" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R23" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S23" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="7" t="str">
+        <x:v>Yo-Chi Double Bay</x:v>
+      </x:c>
+      <x:c r="B24" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C24" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D24" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E24" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F24" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G24" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H24" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I24" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J24" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K24" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L24" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M24" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N24" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O24" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P24" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q24" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R24" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S24" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="7" t="str">
+        <x:v>Yo-Chi Eastland</x:v>
+      </x:c>
+      <x:c r="B25" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C25" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D25" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E25" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F25" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G25" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H25" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I25" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J25" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K25" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L25" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M25" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N25" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O25" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P25" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q25" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R25" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S25" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="7" t="str">
+        <x:v>Yo-Chi Forrest Chase</x:v>
+      </x:c>
+      <x:c r="B26" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C26" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D26" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E26" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F26" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G26" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H26" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I26" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J26" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K26" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L26" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M26" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N26" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O26" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P26" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q26" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R26" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S26" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="7" t="str">
+        <x:v>Yo-Chi Fremantle</x:v>
+      </x:c>
+      <x:c r="B27" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C27" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D27" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E27" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F27" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G27" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H27" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I27" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J27" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K27" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L27" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M27" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N27" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O27" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P27" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q27" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R27" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S27" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="7" t="str">
+        <x:v>Yo-Chi Gasworks</x:v>
+      </x:c>
+      <x:c r="B28" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C28" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D28" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E28" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F28" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G28" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H28" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I28" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J28" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K28" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L28" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M28" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N28" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O28" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P28" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q28" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R28" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S28" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="7" t="str">
+        <x:v>Yo-Chi George St</x:v>
+      </x:c>
+      <x:c r="B29" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C29" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D29" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E29" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F29" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G29" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H29" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I29" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J29" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K29" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L29" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M29" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N29" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O29" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P29" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q29" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R29" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S29" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="7" t="str">
+        <x:v>Yo-Chi Glenelg</x:v>
+      </x:c>
+      <x:c r="B30" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C30" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D30" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E30" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F30" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G30" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H30" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I30" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J30" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K30" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L30" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M30" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N30" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O30" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P30" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q30" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R30" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S30" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="7" t="str">
+        <x:v>Yo-Chi Gouger St</x:v>
+      </x:c>
+      <x:c r="B31" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C31" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D31" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E31" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F31" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G31" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H31" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I31" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J31" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K31" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L31" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M31" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N31" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O31" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P31" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q31" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R31" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S31" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="7" t="str">
+        <x:v>Yo-Chi Harbour Town</x:v>
+      </x:c>
+      <x:c r="B32" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C32" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D32" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E32" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F32" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G32" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H32" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I32" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J32" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K32" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L32" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M32" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N32" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O32" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P32" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q32" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R32" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S32" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="7" t="str">
+        <x:v>Yo-Chi Hawthorn</x:v>
+      </x:c>
+      <x:c r="B33" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C33" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D33" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E33" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F33" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G33" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H33" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I33" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J33" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K33" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L33" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M33" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N33" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O33" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P33" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q33" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R33" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S33" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="7" t="str">
+        <x:v>Yo-Chi Henley Beach</x:v>
+      </x:c>
+      <x:c r="B34" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C34" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D34" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E34" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F34" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G34" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H34" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I34" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J34" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K34" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L34" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M34" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N34" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O34" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P34" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q34" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R34" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S34" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="7" t="str">
+        <x:v>Yo-Chi Highgate</x:v>
+      </x:c>
+      <x:c r="B35" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C35" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D35" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E35" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F35" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G35" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H35" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I35" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J35" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K35" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L35" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M35" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N35" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O35" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P35" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q35" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R35" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S35" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="7" t="str">
+        <x:v>Yo-Chi Highpoint</x:v>
+      </x:c>
+      <x:c r="B36" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C36" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D36" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E36" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F36" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G36" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H36" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I36" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J36" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K36" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L36" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M36" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N36" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O36" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P36" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q36" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R36" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S36" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="7" t="str">
+        <x:v>Yo-Chi Indooroopilly</x:v>
+      </x:c>
+      <x:c r="B37" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C37" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D37" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E37" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F37" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G37" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H37" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I37" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J37" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K37" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L37" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M37" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N37" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O37" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P37" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q37" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R37" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S37" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="7" t="str">
+        <x:v>Yo-Chi Karrinyup</x:v>
+      </x:c>
+      <x:c r="B38" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C38" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D38" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E38" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F38" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G38" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H38" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I38" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J38" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K38" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L38" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M38" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N38" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O38" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P38" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q38" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R38" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S38" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="7" t="str">
+        <x:v>Yo-Chi Kawana Waters</x:v>
+      </x:c>
+      <x:c r="B39" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C39" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D39" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E39" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F39" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G39" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H39" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I39" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J39" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K39" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L39" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M39" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N39" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O39" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P39" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q39" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R39" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S39" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="7" t="str">
+        <x:v>Yo-Chi Lane Cove</x:v>
+      </x:c>
+      <x:c r="B40" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C40" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D40" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E40" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F40" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G40" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H40" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I40" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J40" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K40" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L40" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M40" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N40" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O40" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P40" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q40" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R40" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S40" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="7" t="str">
+        <x:v>Yo-Chi Leederville</x:v>
+      </x:c>
+      <x:c r="B41" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C41" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D41" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E41" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F41" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G41" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H41" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I41" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J41" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K41" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L41" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M41" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N41" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O41" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P41" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q41" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R41" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S41" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="7" t="str">
+        <x:v>Yo-Chi Macquarie</x:v>
+      </x:c>
+      <x:c r="B42" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C42" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D42" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E42" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F42" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G42" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H42" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I42" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J42" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K42" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L42" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M42" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N42" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O42" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P42" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q42" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R42" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S42" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="7" t="str">
+        <x:v>Yo-Chi Malvern</x:v>
+      </x:c>
+      <x:c r="B43" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C43" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D43" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E43" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F43" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G43" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H43" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I43" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J43" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K43" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L43" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M43" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N43" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O43" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P43" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q43" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R43" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S43" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="7" t="str">
+        <x:v>Yo-Chi Mandurah</x:v>
+      </x:c>
+      <x:c r="B44" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C44" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D44" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E44" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F44" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G44" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H44" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I44" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J44" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K44" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L44" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M44" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N44" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O44" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P44" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q44" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R44" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S44" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="7" t="str">
+        <x:v>Yo-Chi Manly</x:v>
+      </x:c>
+      <x:c r="B45" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C45" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D45" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E45" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F45" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G45" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H45" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I45" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J45" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K45" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L45" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M45" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N45" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O45" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P45" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q45" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R45" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S45" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="7" t="str">
+        <x:v>Yo-Chi Mt Gravatt</x:v>
+      </x:c>
+      <x:c r="B46" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C46" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D46" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E46" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F46" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G46" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H46" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I46" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J46" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K46" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L46" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M46" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N46" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O46" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P46" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q46" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R46" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S46" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="7" t="str">
+        <x:v>Yo-Chi Newtown</x:v>
+      </x:c>
+      <x:c r="B47" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C47" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D47" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E47" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F47" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G47" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H47" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I47" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J47" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K47" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L47" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M47" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N47" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O47" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P47" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q47" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R47" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S47" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="7" t="str">
+        <x:v>Yo-Chi Noosa</x:v>
+      </x:c>
+      <x:c r="B48" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C48" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D48" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E48" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F48" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G48" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H48" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I48" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J48" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K48" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L48" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M48" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N48" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O48" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P48" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q48" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R48" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S48" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="7" t="str">
+        <x:v>Yo-Chi Norwood</x:v>
+      </x:c>
+      <x:c r="B49" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C49" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D49" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E49" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F49" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G49" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H49" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I49" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J49" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K49" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L49" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M49" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N49" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O49" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P49" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q49" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R49" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S49" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="7" t="str">
+        <x:v>Yo-Chi Paddington</x:v>
+      </x:c>
+      <x:c r="B50" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C50" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D50" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E50" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F50" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G50" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H50" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I50" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J50" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K50" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L50" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M50" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N50" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O50" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P50" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q50" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R50" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S50" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="7" t="str">
+        <x:v>Yo-Chi Penrith</x:v>
+      </x:c>
+      <x:c r="B51" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C51" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D51" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E51" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F51" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G51" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H51" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I51" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J51" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K51" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L51" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M51" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N51" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O51" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P51" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q51" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R51" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S51" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="7" t="str">
+        <x:v>Yo-Chi Prospect</x:v>
+      </x:c>
+      <x:c r="B52" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C52" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D52" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E52" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F52" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G52" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H52" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I52" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J52" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K52" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L52" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M52" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N52" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O52" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P52" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q52" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R52" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S52" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="7" t="str">
+        <x:v>Yo-Chi QV</x:v>
+      </x:c>
+      <x:c r="B53" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C53" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D53" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E53" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F53" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G53" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H53" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I53" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J53" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K53" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L53" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M53" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N53" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O53" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P53" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q53" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R53" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S53" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="7" t="str">
+        <x:v>Yo-Chi Randwick</x:v>
+      </x:c>
+      <x:c r="B54" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C54" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D54" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E54" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F54" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G54" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H54" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I54" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J54" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K54" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L54" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M54" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N54" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O54" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P54" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q54" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R54" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S54" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="7" t="str">
+        <x:v>Yo-Chi Robina</x:v>
+      </x:c>
+      <x:c r="B55" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C55" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D55" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E55" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F55" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G55" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H55" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I55" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J55" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K55" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L55" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M55" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N55" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O55" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P55" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q55" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R55" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S55" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="7" t="str">
+        <x:v>Yo-Chi Rouse Hill</x:v>
+      </x:c>
+      <x:c r="B56" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C56" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D56" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E56" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F56" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G56" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H56" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I56" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J56" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K56" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L56" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M56" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N56" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O56" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P56" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q56" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R56" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S56" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="7" t="str">
+        <x:v>Yo-Chi Semaphore</x:v>
+      </x:c>
+      <x:c r="B57" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C57" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D57" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E57" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F57" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G57" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H57" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I57" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J57" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K57" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L57" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M57" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N57" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O57" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P57" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q57" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R57" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S57" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="7" t="str">
+        <x:v>Yo-Chi South Perth</x:v>
+      </x:c>
+      <x:c r="B58" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C58" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D58" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E58" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F58" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G58" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H58" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I58" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J58" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K58" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L58" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M58" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N58" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O58" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P58" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q58" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R58" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S58" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="7" t="str">
+        <x:v>Yo-Chi Southbank</x:v>
+      </x:c>
+      <x:c r="B59" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C59" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D59" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E59" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F59" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G59" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H59" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I59" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J59" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K59" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L59" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M59" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N59" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O59" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P59" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q59" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R59" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S59" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="7" t="str">
+        <x:v>Yo-Chi Southland</x:v>
+      </x:c>
+      <x:c r="B60" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C60" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D60" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E60" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F60" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G60" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H60" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I60" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J60" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K60" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L60" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M60" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N60" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O60" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P60" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q60" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R60" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S60" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="7" t="str">
+        <x:v>Yo-Chi Sunshine Plaza</x:v>
+      </x:c>
+      <x:c r="B61" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C61" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D61" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E61" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F61" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G61" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H61" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I61" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J61" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K61" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L61" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M61" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N61" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O61" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P61" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q61" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R61" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S61" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="7" t="str">
+        <x:v>Yo-Chi Surry Hills</x:v>
+      </x:c>
+      <x:c r="B62" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C62" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D62" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E62" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F62" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G62" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H62" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I62" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J62" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K62" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L62" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M62" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N62" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O62" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P62" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q62" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R62" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S62" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="7" t="str">
+        <x:v>Yo-Chi Tea Tree Plaza</x:v>
+      </x:c>
+      <x:c r="B63" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C63" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D63" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E63" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F63" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G63" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H63" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I63" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J63" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K63" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L63" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M63" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N63" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O63" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P63" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q63" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R63" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S63" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="7" t="str">
+        <x:v>Yo-Chi The Esplanade Surfers Paradise</x:v>
+      </x:c>
+      <x:c r="B64" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C64" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D64" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E64" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F64" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G64" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H64" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I64" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J64" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K64" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L64" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M64" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N64" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O64" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P64" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q64" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R64" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S64" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="7" t="str">
+        <x:v>Yo-Chi Top Ryde</x:v>
+      </x:c>
+      <x:c r="B65" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C65" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D65" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E65" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F65" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G65" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H65" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I65" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J65" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K65" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L65" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M65" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N65" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O65" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P65" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q65" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R65" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S65" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="7" t="str">
+        <x:v>Yo-Chi Vic Park</x:v>
+      </x:c>
+      <x:c r="B66" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C66" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D66" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E66" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F66" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G66" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H66" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I66" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J66" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K66" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L66" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M66" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N66" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O66" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P66" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q66" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R66" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S66" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="7" t="str">
+        <x:v>Yo-Chi West End</x:v>
+      </x:c>
+      <x:c r="B67" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C67" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D67" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E67" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F67" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G67" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H67" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I67" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J67" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K67" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L67" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M67" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N67" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O67" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P67" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q67" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R67" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S67" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="7" t="str">
+        <x:v>Yo-Chi Whitford City</x:v>
+      </x:c>
+      <x:c r="B68" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C68" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D68" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E68" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F68" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G68" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H68" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I68" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J68" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K68" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L68" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M68" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N68" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O68" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P68" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q68" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R68" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S68" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="7" t="str">
+        <x:v>Yo-Chi Windsor</x:v>
+      </x:c>
+      <x:c r="B69" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C69" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D69" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E69" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F69" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G69" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H69" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I69" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J69" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K69" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L69" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M69" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N69" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O69" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P69" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q69" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R69" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S69" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="7" t="str">
+        <x:v>Yo-Chi New Venue 01</x:v>
+      </x:c>
+      <x:c r="B70" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C70" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D70" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E70" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F70" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G70" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H70" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I70" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J70" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K70" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L70" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M70" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N70" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O70" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P70" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q70" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R70" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S70" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="7" t="str">
+        <x:v>Yo-Chi New Venue 02</x:v>
+      </x:c>
+      <x:c r="B71" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C71" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D71" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E71" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F71" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G71" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H71" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I71" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J71" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K71" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L71" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M71" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N71" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O71" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P71" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q71" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R71" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S71" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="7" t="str">
+        <x:v>Yo-Chi New Venue 03</x:v>
+      </x:c>
+      <x:c r="B72" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C72" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D72" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E72" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F72" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G72" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H72" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I72" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J72" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K72" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L72" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M72" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N72" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O72" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P72" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q72" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R72" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S72" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="7" t="str">
+        <x:v>Yo-Chi New Venue 04</x:v>
+      </x:c>
+      <x:c r="B73" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C73" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D73" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E73" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F73" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G73" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H73" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I73" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J73" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K73" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L73" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M73" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N73" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O73" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P73" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q73" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R73" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S73" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="7" t="str">
+        <x:v>Yo-Chi New Venue 05</x:v>
+      </x:c>
+      <x:c r="B74" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C74" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D74" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E74" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F74" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G74" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H74" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I74" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J74" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K74" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L74" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M74" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N74" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O74" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P74" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q74" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R74" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S74" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="7" t="str">
+        <x:v>Yo-Chi New Venue 06</x:v>
+      </x:c>
+      <x:c r="B75" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C75" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D75" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E75" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F75" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G75" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H75" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I75" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J75" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K75" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L75" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M75" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N75" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O75" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P75" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q75" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R75" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S75" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="7" t="str">
+        <x:v>Yo-Chi New Venue 07</x:v>
+      </x:c>
+      <x:c r="B76" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C76" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D76" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E76" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F76" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G76" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H76" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I76" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J76" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K76" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L76" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M76" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N76" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O76" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P76" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q76" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R76" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S76" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="7" t="str">
+        <x:v>Yo-Chi New Venue 08</x:v>
+      </x:c>
+      <x:c r="B77" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C77" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D77" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E77" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F77" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G77" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H77" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I77" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J77" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K77" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L77" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M77" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N77" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O77" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P77" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q77" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R77" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S77" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="7" t="str">
+        <x:v>Yo-Chi New Venue 09</x:v>
+      </x:c>
+      <x:c r="B78" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C78" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D78" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E78" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F78" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G78" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H78" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I78" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J78" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K78" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L78" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M78" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N78" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O78" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P78" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q78" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R78" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S78" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="7" t="str">
+        <x:v>Yo-Chi New Venue 10</x:v>
+      </x:c>
+      <x:c r="B79" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C79" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D79" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E79" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F79" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G79" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H79" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I79" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J79" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K79" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L79" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M79" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N79" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O79" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P79" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q79" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R79" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S79" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="7" t="str">
+        <x:v>Yo-Chi New Venue 11</x:v>
+      </x:c>
+      <x:c r="B80" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C80" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D80" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E80" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F80" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G80" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H80" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I80" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J80" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K80" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L80" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M80" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N80" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O80" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P80" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q80" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R80" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S80" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="7" t="str">
+        <x:v>Yo-Chi New Venue 12</x:v>
+      </x:c>
+      <x:c r="B81" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C81" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D81" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E81" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F81" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G81" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H81" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I81" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J81" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K81" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L81" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M81" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N81" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O81" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P81" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q81" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R81" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S81" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="7" t="str">
+        <x:v>Yo-Chi New Venue 13</x:v>
+      </x:c>
+      <x:c r="B82" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C82" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D82" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E82" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F82" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G82" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H82" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I82" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J82" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K82" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L82" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M82" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N82" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O82" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P82" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q82" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R82" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S82" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="7" t="str">
+        <x:v>Yo-Chi New Venue 14</x:v>
+      </x:c>
+      <x:c r="B83" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C83" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D83" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E83" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F83" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G83" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H83" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I83" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J83" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K83" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L83" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M83" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N83" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O83" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P83" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q83" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R83" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S83" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="7" t="str">
+        <x:v>Yo-Chi New Venue 15</x:v>
+      </x:c>
+      <x:c r="B84" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C84" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D84" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E84" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F84" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G84" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H84" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I84" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J84" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K84" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L84" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M84" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N84" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O84" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P84" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q84" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R84" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S84" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="7" t="str">
+        <x:v>Yo-Chi New Venue 16</x:v>
+      </x:c>
+      <x:c r="B85" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C85" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D85" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E85" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F85" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G85" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H85" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I85" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J85" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K85" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L85" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M85" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N85" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O85" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P85" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q85" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R85" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S85" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="7" t="str">
+        <x:v>Yo-Chi New Venue 17</x:v>
+      </x:c>
+      <x:c r="B86" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C86" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D86" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E86" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F86" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G86" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H86" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I86" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J86" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K86" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L86" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M86" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N86" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O86" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P86" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q86" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R86" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S86" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="28" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="5" t="str">
+        <x:v>venue_name</x:v>
+      </x:c>
+      <x:c r="B1" s="5" t="str">
+        <x:v>state</x:v>
+      </x:c>
+      <x:c r="C1" s="5" t="str">
+        <x:v>opening_date</x:v>
+      </x:c>
+      <x:c r="D1" s="10" t="str">
+        <x:v>avg_monthly_sales</x:v>
+      </x:c>
+      <x:c r="E1" s="5" t="str">
+        <x:v>similar_venue</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="7" t="str">
+        <x:v>Yo-Chi New Venue 01</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>VIC</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="n">
+        <x:v>208333</x:v>
+      </x:c>
+      <x:c r="E2" s="7" t="str">
+        <x:v>Yo-Chi Carlton</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="7" t="str">
+        <x:v>Yo-Chi New Venue 02</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="str">
+        <x:v>NSW</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="str">
+        <x:v>2026-09-01</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="n">
+        <x:v>208333</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="str">
+        <x:v>Yo-Chi Bondi</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="7" t="str">
+        <x:v>Yo-Chi New Venue 03</x:v>
+      </x:c>
+      <x:c r="B4" s="7" t="str">
+        <x:v>WA</x:v>
+      </x:c>
+      <x:c r="C4" s="7" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+      <x:c r="D4" s="7" t="n">
+        <x:v>208333</x:v>
+      </x:c>
+      <x:c r="E4" s="7" t="str">
+        <x:v>Yo-Chi Karrinyup</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="7" t="str">
+        <x:v>Yo-Chi New Venue 04</x:v>
+      </x:c>
+      <x:c r="B5" s="7" t="str">
+        <x:v>QLD</x:v>
+      </x:c>
+      <x:c r="C5" s="7" t="str">
+        <x:v>2026-11-01</x:v>
+      </x:c>
+      <x:c r="D5" s="7" t="n">
+        <x:v>208333</x:v>
+      </x:c>
+      <x:c r="E5" s="7" t="str">
+        <x:v>Yo-Chi Albert St</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="7" t="str">
+        <x:v>Yo-Chi New Venue 05</x:v>
+      </x:c>
+      <x:c r="B6" s="7" t="str">
+        <x:v>NSW</x:v>
+      </x:c>
+      <x:c r="C6" s="7" t="str">
+        <x:v>2026-12-01</x:v>
+      </x:c>
+      <x:c r="D6" s="7" t="n">
+        <x:v>208333</x:v>
+      </x:c>
+      <x:c r="E6" s="7" t="str">
+        <x:v>Yo-Chi Manly</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="7" t="str">
+        <x:v>Yo-Chi New Venue 06</x:v>
+      </x:c>
+      <x:c r="B7" s="7" t="str">
+        <x:v>VIC</x:v>
+      </x:c>
+      <x:c r="C7" s="7" t="str">
+        <x:v>2027-01-01</x:v>
+      </x:c>
+      <x:c r="D7" s="7" t="n">
+        <x:v>208333</x:v>
+      </x:c>
+      <x:c r="E7" s="7" t="str">
+        <x:v>Yo-Chi Chadstone</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="7" t="str">
+        <x:v>Yo-Chi New Venue 07</x:v>
+      </x:c>
+      <x:c r="B8" s="7" t="str">
+        <x:v>VIC</x:v>
+      </x:c>
+      <x:c r="C8" s="7" t="str">
+        <x:v>2027-01-01</x:v>
+      </x:c>
+      <x:c r="D8" s="7" t="n">
+        <x:v>208333</x:v>
+      </x:c>
+      <x:c r="E8" s="7" t="str">
+        <x:v>Yo-Chi Southland</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="7" t="str">
+        <x:v>Yo-Chi New Venue 08</x:v>
+      </x:c>
+      <x:c r="B9" s="7" t="str">
+        <x:v>NSW</x:v>
+      </x:c>
+      <x:c r="C9" s="7" t="str">
+        <x:v>2027-02-01</x:v>
+      </x:c>
+      <x:c r="D9" s="7" t="n">
+        <x:v>208333</x:v>
+      </x:c>
+      <x:c r="E9" s="7" t="str">
+        <x:v>Yo-Chi Newtown</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="7" t="str">
+        <x:v>Yo-Chi New Venue 09</x:v>
+      </x:c>
+      <x:c r="B10" s="7" t="str">
+        <x:v>WA</x:v>
+      </x:c>
+      <x:c r="C10" s="7" t="str">
+        <x:v>2027-02-01</x:v>
+      </x:c>
+      <x:c r="D10" s="7" t="n">
+        <x:v>208333</x:v>
+      </x:c>
+      <x:c r="E10" s="7" t="str">
+        <x:v>Yo-Chi Claremont</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="7" t="str">
+        <x:v>Yo-Chi New Venue 10</x:v>
+      </x:c>
+      <x:c r="B11" s="7" t="str">
+        <x:v>QLD</x:v>
+      </x:c>
+      <x:c r="C11" s="7" t="str">
+        <x:v>2027-03-01</x:v>
+      </x:c>
+      <x:c r="D11" s="7" t="n">
+        <x:v>208333</x:v>
+      </x:c>
+      <x:c r="E11" s="7" t="str">
+        <x:v>Yo-Chi Broadbeach</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="7" t="str">
+        <x:v>Yo-Chi New Venue 11</x:v>
+      </x:c>
+      <x:c r="B12" s="7" t="str">
+        <x:v>QLD</x:v>
+      </x:c>
+      <x:c r="C12" s="7" t="str">
+        <x:v>2027-03-01</x:v>
+      </x:c>
+      <x:c r="D12" s="7" t="n">
+        <x:v>208333</x:v>
+      </x:c>
+      <x:c r="E12" s="7" t="str">
+        <x:v>Yo-Chi Robina</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="7" t="str">
+        <x:v>Yo-Chi New Venue 12</x:v>
+      </x:c>
+      <x:c r="B13" s="7" t="str">
+        <x:v>NSW</x:v>
+      </x:c>
+      <x:c r="C13" s="7" t="str">
+        <x:v>2027-04-01</x:v>
+      </x:c>
+      <x:c r="D13" s="7" t="n">
+        <x:v>208333</x:v>
+      </x:c>
+      <x:c r="E13" s="7" t="str">
+        <x:v>Yo-Chi Surry Hills</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="7" t="str">
+        <x:v>Yo-Chi New Venue 13</x:v>
+      </x:c>
+      <x:c r="B14" s="7" t="str">
+        <x:v>NSW</x:v>
+      </x:c>
+      <x:c r="C14" s="7" t="str">
+        <x:v>2027-04-01</x:v>
+      </x:c>
+      <x:c r="D14" s="7" t="n">
+        <x:v>208333</x:v>
+      </x:c>
+      <x:c r="E14" s="7" t="str">
+        <x:v>Yo-Chi Chatswood</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="7" t="str">
+        <x:v>Yo-Chi New Venue 14</x:v>
+      </x:c>
+      <x:c r="B15" s="7" t="str">
+        <x:v>NSW</x:v>
+      </x:c>
+      <x:c r="C15" s="7" t="str">
+        <x:v>2027-05-01</x:v>
+      </x:c>
+      <x:c r="D15" s="7" t="n">
+        <x:v>208333</x:v>
+      </x:c>
+      <x:c r="E15" s="7" t="str">
+        <x:v>Yo-Chi Penrith</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="7" t="str">
+        <x:v>Yo-Chi New Venue 15</x:v>
+      </x:c>
+      <x:c r="B16" s="7" t="str">
+        <x:v>WA</x:v>
+      </x:c>
+      <x:c r="C16" s="7" t="str">
+        <x:v>2027-05-01</x:v>
+      </x:c>
+      <x:c r="D16" s="7" t="n">
+        <x:v>208333</x:v>
+      </x:c>
+      <x:c r="E16" s="7" t="str">
+        <x:v>Yo-Chi Fremantle</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="7" t="str">
+        <x:v>Yo-Chi New Venue 16</x:v>
+      </x:c>
+      <x:c r="B17" s="7" t="str">
+        <x:v>SA</x:v>
+      </x:c>
+      <x:c r="C17" s="7" t="str">
+        <x:v>2027-06-01</x:v>
+      </x:c>
+      <x:c r="D17" s="7" t="n">
+        <x:v>208333</x:v>
+      </x:c>
+      <x:c r="E17" s="7" t="str">
+        <x:v>Yo-Chi Glenelg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="7" t="str">
+        <x:v>Yo-Chi New Venue 17</x:v>
+      </x:c>
+      <x:c r="B18" s="7" t="str">
+        <x:v>QLD</x:v>
+      </x:c>
+      <x:c r="C18" s="7" t="str">
+        <x:v>2027-06-01</x:v>
+      </x:c>
+      <x:c r="D18" s="7" t="n">
+        <x:v>208333</x:v>
+      </x:c>
+      <x:c r="E18" s="7" t="str">
+        <x:v>Yo-Chi Indooroopilly</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
